--- a/Assets/Config/Holmas_AgencyBuildingTable.xlsx
+++ b/Assets/Config/Holmas_AgencyBuildingTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Holmas\Assets\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9112CCEC-66BD-493A-B9DF-E6AC75AFC788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29CBDAB-4BAD-4E45-8DC5-BAA77F6E8A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -399,289 +399,16 @@
     <t>2764;3686;4608;5529;6451|3456;4608;5760;6912;8064|4147;5529;6912;8294;9676</t>
   </si>
   <si>
-    <t>10752;14336;17920;21504;25088|13440;17920;22400;26880;31360|16128;21504;26880;32256;37632</t>
-  </si>
-  <si>
-    <t>14592;19456;24320;29184;34048|18240;24320;30400;36480;42560|21888;29184;36480;43776;51072</t>
-  </si>
-  <si>
-    <t>23616;31488;39360;47232;55104|29520;39360;49200;59040;68880|35424;47232;59040;70848;82656</t>
-  </si>
-  <si>
-    <t>33792;45056;56320;67584;78848|42240;56320;70400;84480;98560|50688;67584;84480;101376;118272</t>
-  </si>
-  <si>
-    <t>45120;60160;75200;90240;105280|56400;75200;94000;112800;131600|67680;90240;112800;135360;157920</t>
-  </si>
-  <si>
-    <t>57600;76800;96000;115200;134400|72000;96000;120000;144000;168000|86400;115200;144000;172800;201600</t>
-  </si>
-  <si>
-    <t>71232;94976;118720;142464;166208|89040;118720;148400;178080;207760|106848;142464;178080;213696;249312</t>
-  </si>
-  <si>
-    <t>86016;114688;143360;172032;200704|107520;143360;179200;215040;250880|129024;172032;215040;258048;301056</t>
-  </si>
-  <si>
-    <t>101952;135936;169920;203904;237888|127440;169920;212400;254880;297360|152928;203904;254880;305856;356832</t>
-  </si>
-  <si>
-    <t>119040;158720;198400;238080;277760|148800;198400;248000;297600;347200|178560;238080;297600;357120;416640</t>
-  </si>
-  <si>
-    <t>137280;183040;228800;274560;320320|171600;228800;286000;343200;400400|205920;274560;343200;411840;480480</t>
-  </si>
-  <si>
-    <t>156672;208896;261120;313344;365568|195840;261120;326400;391680;456960|235008;313344;391680;470016;548352</t>
-  </si>
-  <si>
-    <t>177216;236288;295360;354432;413504|221520;295360;369200;443040;516880|265824;354432;443040;531648;620256</t>
-  </si>
-  <si>
-    <t>198912;265216;331520;397824;464128|248640;331520;414400;497280;580160|298368;397824;497280;596736;696192</t>
-  </si>
-  <si>
-    <t>295680;394240;492800;591360;689920|369600;492800;616000;739200;862400|443520;591360;739200;887040;1034880</t>
-  </si>
-  <si>
     <t>504000;672000;840000;1008000;1176000|630000;840000;1050000;1260000;1470000|756000;1008000;1260000;1512000;1764000</t>
   </si>
   <si>
-    <t>540672;720896;901120;1081344;1261568|675840;901120;1126400;1351680;1576960|811008;1081344;1351680;1622016;1892352</t>
-  </si>
-  <si>
-    <t>578496;771328;964160;1156992;1349824|723120;964160;1205200;1446240;1687280|867744;1156992;1446240;1735488;2024736</t>
-  </si>
-  <si>
-    <t>617472;823296;1029120;1234944;1440768|771840;1029120;1286400;1543680;1800960|926208;1234944;1543680;1852416;2161152</t>
-  </si>
-  <si>
-    <t>657600;876800;1096000;1315200;1534400|822000;1096000;1370000;1644000;1918000|986400;1315200;1644000;1972800;2301600</t>
-  </si>
-  <si>
-    <t>698880;931840;1164800;1397760;1630720|873600;1164800;1456000;1747200;2038400|1048320;1397760;1747200;2096640;2446080</t>
-  </si>
-  <si>
-    <t>741312;988416;1235520;1482624;1729728|926640;1235520;1544400;1853280;2162160|1111968;1482624;1853280;2223936;2594592</t>
-  </si>
-  <si>
-    <t>784896;1046528;1308160;1569792;1831424|981120;1308160;1635200;1962240;2289280|1177344;1569792;1962240;2354688;2747136</t>
-  </si>
-  <si>
-    <t>829632;1106176;1382720;1659264;1935808|1037040;1382720;1728400;2074080;2419760|1244448;1659264;2074080;2488896;2903712</t>
-  </si>
-  <si>
-    <t>1167360;1556480;1945600;2334720;2723840|1459200;1945600;2432000;2918400;3404800|1751040;2334720;2918400;3502080;4085760</t>
-  </si>
-  <si>
-    <t>1220160;1626880;2033600;2440320;2847040|1525200;2033600;2542000;3050400;3558800|1830240;2440320;3050400;3660480;4270560</t>
-  </si>
-  <si>
-    <t>1274112;1698816;2123520;2548224;2972928|1592640;2123520;2654400;3185280;3716160|1911168;2548224;3185280;3822336;4459392</t>
-  </si>
-  <si>
-    <t>1329216;1772288;2215360;2658432;3101504|1661520;2215360;2769200;3323040;3876880|1993824;2658432;3323040;3987648;4652256</t>
-  </si>
-  <si>
-    <t>1385472;1847296;2309120;2770944;3232768|1731840;2309120;2886400;3463680;4040960|2078208;2770944;3463680;4156416;4849152</t>
-  </si>
-  <si>
-    <t>1442880;1923840;2404800;2885760;3366720|1803600;2404800;3006000;3607200;4208400|2164320;2885760;3607200;4328640;5050080</t>
-  </si>
-  <si>
-    <t>1501440;2001920;2502400;3002880;3503360|1876800;2502400;3128000;3753600;4379200|2252160;3002880;3753600;4504320;5255040</t>
-  </si>
-  <si>
-    <t>1561152;2081536;2601920;3122304;3642688|1951440;2601920;3252400;3902880;4553360|2341728;3122304;3902880;4683456;5464032</t>
-  </si>
-  <si>
-    <t>1622016;2162688;2703360;3244032;3784704|2027520;2703360;3379200;4055040;4730880|2433024;3244032;4055040;4866048;5677056</t>
-  </si>
-  <si>
-    <t>1684032;2245376;2806720;3368064;3929408|2105040;2806720;3508400;4210080;4911760|2526048;3368064;4210080;5052096;5894112</t>
-  </si>
-  <si>
-    <t>2096640;2795520;3494400;4193280;4892160|2620800;3494400;4368000;5241600;6115200|3144960;4193280;5241600;6289920;7338240</t>
-  </si>
-  <si>
-    <t>4040640;5387520;6734400;8081280;9428160|5050800;6734400;8418000;10101600;11785200|6060960;8081280;10101600;12121920;14142240</t>
-  </si>
-  <si>
-    <t>4166400;5555200;6944000;8332800;9721600|5208000;6944000;8680000;10416000;12152000|6249600;8332800;10416000;12499200;14582400</t>
-  </si>
-  <si>
-    <t>4294080;5725440;7156800;8588160;10019520|5367600;7156800;8946000;10735200;12524400|6441120;8588160;10735200;12882240;15029280</t>
-  </si>
-  <si>
-    <t>4423680;5898240;7372800;8847360;10321920|5529600;7372800;9216000;11059200;12902400|6635520;8847360;11059200;13271040;15482880</t>
-  </si>
-  <si>
-    <t>4555200;6073600;7592000;9110400;10628800|5694000;7592000;9490000;11388000;13286000|6832800;9110400;11388000;13665600;15943200</t>
-  </si>
-  <si>
-    <t>4688640;6251520;7814400;9377280;10940160|5860800;7814400;9768000;11721600;13675200|7032960;9377280;11721600;14065920;16410240</t>
-  </si>
-  <si>
     <t>4824000;6432000;8040000;9648000;11256000|6030000;8040000;10050000;12060000;14070000|7236000;9648000;12060000;14472000;16884000</t>
   </si>
   <si>
-    <t>4961280;6615040;8268800;9922560;11576320|6201600;8268800;10336000;12403200;14470400|7441920;9922560;12403200;14883840;17364480</t>
-  </si>
-  <si>
-    <t>5100480;6800640;8500800;10200960;11901120|6375600;8500800;10626000;12751200;14876400|7650720;10200960;12751200;15301440;17851680</t>
-  </si>
-  <si>
-    <t>5990400;7987200;9984000;11980800;13977600|7488000;9984000;12480000;14976000;17472000|8985600;11980800;14976000;17971200;20966400</t>
-  </si>
-  <si>
-    <t>6143040;8190720;10238400;12286080;14333760|7678800;10238400;12798000;15357600;17917200|9214560;12286080;15357600;18429120;21500640</t>
-  </si>
-  <si>
-    <t>6297600;8396800;10496000;12595200;14694400|7872000;10496000;13120000;15744000;18368000|9446400;12595200;15744000;18892800;22041600</t>
-  </si>
-  <si>
-    <t>6454080;8605440;10756800;12908160;15059520|8067600;10756800;13446000;16135200;18824400|9681120;12908160;16135200;19362240;22589280</t>
-  </si>
-  <si>
-    <t>6612480;8816640;11020800;13224960;15429120|8265600;11020800;13776000;16531200;19286400|9918720;13224960;16531200;19837440;23143680</t>
-  </si>
-  <si>
-    <t>6772800;9030400;11288000;13545600;15803200|8466000;11288000;14110000;16932000;19754000|10159200;13545600;16932000;20318400;23704800</t>
-  </si>
-  <si>
-    <t>6935040;9246720;11558400;13870080;16181760|8668800;11558400;14448000;17337600;20227200|10402560;13870080;17337600;20805120;24272640</t>
-  </si>
-  <si>
-    <t>7099200;9465600;11832000;14198400;16564800|8874000;11832000;14790000;17748000;20706000|10648800;14198400;17748000;21297600;24847200</t>
-  </si>
-  <si>
-    <t>7265280;9687040;12108800;14530560;16952320|9081600;12108800;15136000;18163200;21190400|10897920;14530560;18163200;21795840;25428480</t>
-  </si>
-  <si>
-    <t>7433280;9911040;12388800;14866560;17344320|9291600;12388800;15486000;18583200;21680400|11149920;14866560;18583200;22299840;26016480</t>
-  </si>
-  <si>
     <t>8448000;11264000;14080000;16896000;19712000|10560000;14080000;17600000;21120000;24640000|12672000;16896000;21120000;25344000;29568000</t>
   </si>
   <si>
-    <t>11732160;15642880;19553600;23464320;27375040|14665200;19553600;24442000;29330400;34218800|17598240;23464320;29330400;35196480;41062560</t>
-  </si>
-  <si>
-    <t>11965824;15954432;19943040;23931648;27920256|14957280;19943040;24928800;29914560;34900320|17948736;23931648;29914560;35897472;41880384</t>
-  </si>
-  <si>
-    <t>12201792;16269056;20336320;24403584;28470848|15252240;20336320;25420400;30504480;35588560|18302688;24403584;30504480;36605376;42706272</t>
-  </si>
-  <si>
-    <t>12440064;16586752;20733440;24880128;29026816|15550080;20733440;25916800;31100160;36283520|18660096;24880128;31100160;37320192;43540224</t>
-  </si>
-  <si>
-    <t>12680640;16907520;21134400;25361280;29588160|15850800;21134400;26418000;31701600;36985200|19020960;25361280;31701600;38041920;44382240</t>
-  </si>
-  <si>
-    <t>12923520;17231360;21539200;25847040;30154880|16154400;21539200;26924000;32308800;37693600|19385280;25847040;32308800;38770560;45232320</t>
-  </si>
-  <si>
-    <t>13168704;17558272;21947840;26337408;30726976|16460880;21947840;27434800;32921760;38408720|19753056;26337408;32921760;39506112;46090464</t>
-  </si>
-  <si>
-    <t>13416192;17888256;22360320;26832384;31304448|16770240;22360320;27950400;33540480;39130560|20124288;26832384;33540480;40248576;46956672</t>
-  </si>
-  <si>
-    <t>13665984;18221312;22776640;27331968;31887296|17082480;22776640;28470800;34164960;39859120|20498976;27331968;34164960;40997952;47830944</t>
-  </si>
-  <si>
-    <t>15183360;20244480;25305600;30366720;35427840|18979200;25305600;31632000;37958400;44284800|22775040;30366720;37958400;45550080;53141760</t>
-  </si>
-  <si>
-    <t>15449280;20599040;25748800;30898560;36048320|19311600;25748800;32186000;38623200;45060400|23173920;30898560;38623200;46347840;54072480</t>
-  </si>
-  <si>
-    <t>15717504;20956672;26195840;31435008;36674176|19646880;26195840;32744800;39293760;45842720|23576256;31435008;39293760;47152512;55011264</t>
-  </si>
-  <si>
-    <t>15988032;21317376;26646720;31976064;37305408|19985040;26646720;33308400;39970080;46631760|23982048;31976064;39970080;47964096;55958112</t>
-  </si>
-  <si>
-    <t>16260864;21681152;27101440;32521728;37942016|20326080;27101440;33876800;40652160;47427520|24391296;32521728;40652160;48782592;56913024</t>
-  </si>
-  <si>
     <t>16536000;22048000;27560000;33072000;38584000|20670000;27560000;34450000;41340000;48230000|24804000;33072000;41340000;49608000;57876000</t>
-  </si>
-  <si>
-    <t>16813440;22417920;28022400;33626880;39231360|21016800;28022400;35028000;42033600;49039200|25220160;33626880;42033600;50440320;58847040</t>
-  </si>
-  <si>
-    <t>17093184;22790912;28488640;34186368;39884096|21366480;28488640;35610800;42732960;49855120|25639776;34186368;42732960;51279552;59826144</t>
-  </si>
-  <si>
-    <t>17375232;23166976;28958720;34750464;40542208|21719040;28958720;36198400;43438080;50677760|26062848;34750464;43438080;52125696;60813312</t>
-  </si>
-  <si>
-    <t>17659584;23546112;29432640;35319168;41205696|22074480;29432640;36790800;44148960;51507120|26489376;35319168;44148960;52978752;61808544</t>
-  </si>
-  <si>
-    <t>19326720;25768960;32211200;38653440;45095680|24158400;32211200;40264000;48316800;56369600|28990080;38653440;48316800;57980160;67643520</t>
-  </si>
-  <si>
-    <t>19627200;26169600;32712000;39254400;45796800|24534000;32712000;40890000;49068000;57246000|29440800;39254400;49068000;58881600;68695200</t>
-  </si>
-  <si>
-    <t>19929984;26573312;33216640;39859968;46503296|24912480;33216640;41520800;49824960;58129120|29894976;39859968;49824960;59789952;69754944</t>
-  </si>
-  <si>
-    <t>20235072;26980096;33725120;40470144;47215168|25293840;33725120;42156400;50587680;59018960|30352608;40470144;50587680;60705216;70822752</t>
-  </si>
-  <si>
-    <t>20542464;27389952;34237440;41084928;47932416|25678080;34237440;42796800;51356160;59915520|30813696;41084928;51356160;61627392;71898624</t>
-  </si>
-  <si>
-    <t>20852160;27802880;34753600;41704320;48655040|26065200;34753600;43442000;52130400;60818800|31278240;41704320;52130400;62556480;72982560</t>
-  </si>
-  <si>
-    <t>21164160;28218880;35273600;42328320;49383040|26455200;35273600;44092000;52910400;61728800|31746240;42328320;52910400;63492480;74074560</t>
-  </si>
-  <si>
-    <t>21478464;28637952;35797440;42956928;50116416|26848080;35797440;44746800;53696160;62645520|32217696;42956928;53696160;64435392;75174624</t>
-  </si>
-  <si>
-    <t>21795072;29060096;36325120;43590144;50855168|27243840;36325120;45406400;54487680;63568960|32692608;43590144;54487680;65385216;76282752</t>
-  </si>
-  <si>
-    <t>22113984;29485312;36856640;44227968;51599296|27642480;36856640;46070800;55284960;64499120|33170976;44227968;55284960;66341952;77398944</t>
-  </si>
-  <si>
-    <t>23930880;31907840;39884800;47861760;55838720|29913600;39884800;49856000;59827200;69798400|35896320;47861760;59827200;71792640;83758080</t>
-  </si>
-  <si>
-    <t>24265920;32354560;40443200;48531840;56620480|30332400;40443200;50554000;60664800;70775600|36398880;48531840;60664800;72797760;84930720</t>
-  </si>
-  <si>
-    <t>24603264;32804352;41005440;49206528;57407616|30754080;41005440;51256800;61508160;71759520|36904896;49206528;61508160;73809792;86111424</t>
-  </si>
-  <si>
-    <t>24942912;33257216;41571520;49885824;58200128|31178640;41571520;51964400;62357280;72750160|37414368;49885824;62357280;74828736;87300192</t>
-  </si>
-  <si>
-    <t>25284864;33713152;42141440;50569728;58998016|31606080;42141440;52676800;63212160;73747520|37927296;50569728;63212160;75854592;88497024</t>
-  </si>
-  <si>
-    <t>25629120;34172160;42715200;51258240;59801280|32036400;42715200;53394000;64072800;74751600|38443680;51258240;64072800;76887360;89701920</t>
-  </si>
-  <si>
-    <t>25975680;34634240;43292800;51951360;60609920|32469600;43292800;54116000;64939200;75762400|38963520;51951360;64939200;77927040;90914880</t>
-  </si>
-  <si>
-    <t>26324544;35099392;43874240;52649088;61423936|32905680;43874240;54842800;65811360;76779920|39486816;52649088;65811360;78973632;92135904</t>
-  </si>
-  <si>
-    <t>26675712;35567616;44459520;53351424;62243328|33344640;44459520;55574400;66689280;77804160|40013568;53351424;66689280;80027136;93364992</t>
-  </si>
-  <si>
-    <t>27029184;36038912;45048640;54058368;63068096|33786480;45048640;56310800;67572960;78835120|40543776;54058368;67572960;81087552;94602144</t>
-  </si>
-  <si>
-    <t>28995840;38661120;48326400;57991680;67656960|36244800;48326400;60408000;72489600;84571200|43493760;57991680;72489600;86987520;101485440</t>
   </si>
   <si>
     <t>3;3;3</t>
@@ -998,6 +725,279 @@
   </si>
   <si>
     <t>玫瑰谷田庄</t>
+  </si>
+  <si>
+    <t>10000;14000;17000;21000;25000|13000;17000;22000;26000;31000|16000;21000;26000;32000;37000</t>
+  </si>
+  <si>
+    <t>14000;19000;24000;29000;34000|18000;24000;30000;36000;42000|21000;29000;36000;43000;51000</t>
+  </si>
+  <si>
+    <t>23000;31000;39000;47000;55000|29000;39000;49000;59000;68000|35000;47000;59000;70000;82000</t>
+  </si>
+  <si>
+    <t>33000;45000;56000;67000;78000|42000;56000;70000;84000;98000|50000;67000;84000;101000;118000</t>
+  </si>
+  <si>
+    <t>45000;60000;75000;90000;105000|56000;75000;94000;112000;131000|67000;90000;112000;135000;157000</t>
+  </si>
+  <si>
+    <t>57000;76000;96000;115000;134000|72000;96000;120000;144000;168000|86000;115000;144000;172000;201000</t>
+  </si>
+  <si>
+    <t>71000;94000;118000;142000;166000|89000;118000;148000;178000;207000|106000;142000;178000;213000;249000</t>
+  </si>
+  <si>
+    <t>86000;114000;143000;172000;200000|107000;143000;179000;215000;250000|129000;172000;215000;258000;301000</t>
+  </si>
+  <si>
+    <t>101000;135000;169000;203000;237000|127000;169000;212000;254000;297000|152000;203000;254000;305000;356000</t>
+  </si>
+  <si>
+    <t>119000;158000;198000;238000;277000|148000;198000;248000;297000;347000|178000;238000;297000;357000;416000</t>
+  </si>
+  <si>
+    <t>137000;183000;228000;274000;320000|171000;228000;286000;343000;400000|205000;274000;343000;411000;480000</t>
+  </si>
+  <si>
+    <t>156000;208000;261000;313000;365000|195000;261000;326000;391000;456000|235000;313000;391000;470000;548000</t>
+  </si>
+  <si>
+    <t>177000;236000;295000;354000;413000|221000;295000;369000;443000;516000|265000;354000;443000;531000;620000</t>
+  </si>
+  <si>
+    <t>198000;265000;331000;397000;464000|248000;331000;414000;497000;580000|298000;397000;497000;596000;696000</t>
+  </si>
+  <si>
+    <t>295000;394000;492000;591000;689000|369000;492000;616000;739000;862000|443000;591000;739000;887000;1034000</t>
+  </si>
+  <si>
+    <t>540000;720000;901000;1081000;1261000|675000;901000;1126000;1351000;1576000|811000;1081000;1351000;1622000;1892000</t>
+  </si>
+  <si>
+    <t>578000;771000;964000;1156000;1349000|723000;964000;1205000;1446000;1687000|867000;1156000;1446000;1735000;2024000</t>
+  </si>
+  <si>
+    <t>617000;823000;1029000;1234000;1440000|771000;1029000;1286000;1543000;1800000|926000;1234000;1543000;1852000;2161000</t>
+  </si>
+  <si>
+    <t>657000;876000;1096000;1315000;1534000|822000;1096000;1370000;1644000;1918000|986000;1315000;1644000;1972000;2301000</t>
+  </si>
+  <si>
+    <t>698000;931000;1164000;1397000;1630000|873000;1164000;1456000;1747000;2038000|1048000;1397000;1747000;2096000;2446000</t>
+  </si>
+  <si>
+    <t>741000;988000;1235000;1482000;1729000|926000;1235000;1544000;1853000;2162000|1111000;1482000;1853000;2223000;2594000</t>
+  </si>
+  <si>
+    <t>784000;1046000;1308000;1569000;1831000|981000;1308000;1635000;1962000;2289000|1177000;1569000;1962000;2354000;2747000</t>
+  </si>
+  <si>
+    <t>829000;1106000;1382000;1659000;1935000|1037000;1382000;1728000;2074000;2419000|1244000;1659000;2074000;2488000;2903000</t>
+  </si>
+  <si>
+    <t>1167000;1556000;1945000;2334000;2723000|1459000;1945000;2432000;2918000;3404000|1751000;2334000;2918000;3502000;4085000</t>
+  </si>
+  <si>
+    <t>1220000;1626000;2033000;2440000;2847000|1525000;2033000;2542000;3050000;3558000|1830000;2440000;3050000;3660000;4270000</t>
+  </si>
+  <si>
+    <t>1274000;1698000;2123000;2548000;2972000|1592000;2123000;2654000;3185000;3716000|1911000;2548000;3185000;3822000;4459000</t>
+  </si>
+  <si>
+    <t>1329000;1772000;2215000;2658000;3101000|1661000;2215000;2769000;3323000;3876000|1993000;2658000;3323000;3987000;4652000</t>
+  </si>
+  <si>
+    <t>1385000;1847000;2309000;2770000;3232000|1731000;2309000;2886000;3463000;4040000|2078000;2770000;3463000;4156000;4849000</t>
+  </si>
+  <si>
+    <t>1442000;1923000;2404000;2885000;3366000|1803000;2404000;3006000;3607000;4208000|2164000;2885000;3607000;4328000;5050000</t>
+  </si>
+  <si>
+    <t>1501000;2001000;2502000;3002000;3503000|1876000;2502000;3128000;3753000;4379000|2252000;3002000;3753000;4504000;5255000</t>
+  </si>
+  <si>
+    <t>1561000;2081000;2601000;3122000;3642000|1951000;2601000;3252000;3902000;4553000|2341000;3122000;3902000;4683000;5464000</t>
+  </si>
+  <si>
+    <t>1622000;2162000;2703000;3244000;3784000|2027000;2703000;3379000;4055000;4730000|2433000;3244000;4055000;4866000;5677000</t>
+  </si>
+  <si>
+    <t>1684000;2245000;2806000;3368000;3929000|2105000;2806000;3508000;4210000;4911000|2526000;3368000;4210000;5052000;5894000</t>
+  </si>
+  <si>
+    <t>2096000;2795000;3494000;4193000;4892000|2620000;3494000;4368000;5241000;6115000|3144000;4193000;5241000;6289000;7338000</t>
+  </si>
+  <si>
+    <t>4040000;5387000;6734000;8081000;9428000|5050000;6734000;8418000;10101000;11785000|6060000;8081000;10101000;12121000;14142000</t>
+  </si>
+  <si>
+    <t>4166000;5555000;6944000;8332000;9721000|5208000;6944000;8680000;10416000;12152000|6249000;8332000;10416000;12499000;14582000</t>
+  </si>
+  <si>
+    <t>4294000;5725000;7156000;8588000;10019000|5367000;7156000;8946000;10735000;12524000|6441000;8588000;10735000;12882000;15029000</t>
+  </si>
+  <si>
+    <t>4423000;5898000;7372000;8847000;10321000|5529000;7372000;9216000;11059000;12902000|6635000;8847000;11059000;13271000;15482000</t>
+  </si>
+  <si>
+    <t>4555000;6073000;7592000;9110000;10628000|5694000;7592000;9490000;11388000;13286000|6832000;9110000;11388000;13665000;15943000</t>
+  </si>
+  <si>
+    <t>4688000;6251000;7814000;9377000;10940000|5860000;7814000;9768000;11721000;13675000|7032000;9377000;11721000;14065000;16410000</t>
+  </si>
+  <si>
+    <t>4961000;6615000;8268000;9922000;11576000|6201000;8268000;10336000;12403000;14470000|7441000;9922000;12403000;14883000;17364000</t>
+  </si>
+  <si>
+    <t>5100000;6800000;8500000;10200000;11901000|6375000;8500000;10626000;12751000;14876000|7650000;10200000;12751000;15301000;17851000</t>
+  </si>
+  <si>
+    <t>5990000;7987000;9984000;11980000;13977000|7488000;9984000;12480000;14976000;17472000|8985000;11980000;14976000;17971000;20966000</t>
+  </si>
+  <si>
+    <t>6143000;8190000;10238000;12286000;14333000|7678000;10238000;12798000;15357000;17917000|9214000;12286000;15357000;18429000;21500000</t>
+  </si>
+  <si>
+    <t>6297000;8396000;10496000;12595000;14694000|7872000;10496000;13120000;15744000;18368000|9446000;12595000;15744000;18892000;22041000</t>
+  </si>
+  <si>
+    <t>6454000;8605000;10756000;12908000;15059000|8067000;10756000;13446000;16135000;18824000|9681000;12908000;16135000;19362000;22589000</t>
+  </si>
+  <si>
+    <t>6612000;8816000;11020000;13224000;15429000|8265000;11020000;13776000;16531000;19286000|9918000;13224000;16531000;19837000;23143000</t>
+  </si>
+  <si>
+    <t>6772000;9030000;11288000;13545000;15803000|8466000;11288000;14110000;16932000;19754000|10159000;13545000;16932000;20318000;23704000</t>
+  </si>
+  <si>
+    <t>6935000;9246000;11558000;13870000;16181000|8668000;11558000;14448000;17337000;20227000|10402000;13870000;17337000;20805000;24272000</t>
+  </si>
+  <si>
+    <t>7099000;9465000;11832000;14198000;16564000|8874000;11832000;14790000;17748000;20706000|10648000;14198000;17748000;21297000;24847000</t>
+  </si>
+  <si>
+    <t>7265000;9687000;12108000;14530000;16952000|9081000;12108000;15136000;18163000;21190000|10897000;14530000;18163000;21795000;25428000</t>
+  </si>
+  <si>
+    <t>7433000;9911000;12388000;14866000;17344000|9291000;12388000;15486000;18583000;21680000|11149000;14866000;18583000;22299000;26016000</t>
+  </si>
+  <si>
+    <t>11732000;15642000;19553000;23464000;27375000|14665000;19553000;24442000;29330000;34218000|17598000;23464000;29330000;35196000;41062000</t>
+  </si>
+  <si>
+    <t>11965000;15954000;19943000;23931000;27920000|14957000;19943000;24928000;29914000;34900000|17948000;23931000;29914000;35897000;41880000</t>
+  </si>
+  <si>
+    <t>12201000;16269000;20336000;24403000;28470000|15252000;20336000;25420000;30504000;35588000|18302000;24403000;30504000;36605000;42706000</t>
+  </si>
+  <si>
+    <t>12440000;16586000;20733000;24880000;29026000|15550000;20733000;25916000;31100000;36283000|18660000;24880000;31100000;37320000;43540000</t>
+  </si>
+  <si>
+    <t>12680000;16907000;21134000;25361000;29588000|15850000;21134000;26418000;31701000;36985000|19020000;25361000;31701000;38041000;44382000</t>
+  </si>
+  <si>
+    <t>12923000;17231000;21539000;25847000;30154000|16154000;21539000;26924000;32308000;37693000|19385000;25847000;32308000;38770000;45232000</t>
+  </si>
+  <si>
+    <t>13168000;17558000;21947000;26337000;30726000|16460000;21947000;27434000;32921000;38408000|19753000;26337000;32921000;39506000;46090000</t>
+  </si>
+  <si>
+    <t>13416000;17888000;22360000;26832000;31304000|16770000;22360000;27950000;33540000;39130000|20124000;26832000;33540000;40248000;46956000</t>
+  </si>
+  <si>
+    <t>13665000;18221000;22776000;27331000;31887000|17082000;22776000;28470000;34164000;39859000|20498000;27331000;34164000;40997000;47830000</t>
+  </si>
+  <si>
+    <t>15183000;20244000;25305000;30366000;35427000|18979000;25305000;31632000;37958000;44284000|22775000;30366000;37958000;45550000;53141000</t>
+  </si>
+  <si>
+    <t>15449000;20599000;25748000;30898000;36048000|19311000;25748000;32186000;38623000;45060000|23173000;30898000;38623000;46347000;54072000</t>
+  </si>
+  <si>
+    <t>15717000;20956000;26195000;31435000;36674000|19646000;26195000;32744000;39293000;45842000|23576000;31435000;39293000;47152000;55011000</t>
+  </si>
+  <si>
+    <t>15988000;21317000;26646000;31976000;37305000|19985000;26646000;33308000;39970000;46631000|23982000;31976000;39970000;47964000;55958000</t>
+  </si>
+  <si>
+    <t>16260000;21681000;27101000;32521000;37942000|20326000;27101000;33876000;40652000;47427000|24391000;32521000;40652000;48782000;56913000</t>
+  </si>
+  <si>
+    <t>16813000;22417000;28022000;33626000;39231000|21016000;28022000;35028000;42033000;49039000|25220000;33626000;42033000;50440000;58847000</t>
+  </si>
+  <si>
+    <t>17093000;22790000;28488000;34186000;39884000|21366000;28488000;35610000;42732000;49855000|25639000;34186000;42732000;51279000;59826000</t>
+  </si>
+  <si>
+    <t>17375000;23166000;28958000;34750000;40542000|21719000;28958000;36198000;43438000;50677000|26062000;34750000;43438000;52125000;60813000</t>
+  </si>
+  <si>
+    <t>17659000;23546000;29432000;35319000;41205000|22074000;29432000;36790000;44148000;51507000|26489000;35319000;44148000;52978000;61808000</t>
+  </si>
+  <si>
+    <t>19326000;25768000;32211000;38653000;45095000|24158000;32211000;40264000;48316000;56369000|28990000;38653000;48316000;57980000;67643000</t>
+  </si>
+  <si>
+    <t>19627000;26169000;32712000;39254000;45796000|24534000;32712000;40890000;49068000;57246000|29440000;39254000;49068000;58881000;68695000</t>
+  </si>
+  <si>
+    <t>19929000;26573000;33216000;39859000;46503000|24912000;33216000;41520000;49824000;58129000|29894000;39859000;49824000;59789000;69754000</t>
+  </si>
+  <si>
+    <t>20235000;26980000;33725000;40470000;47215000|25293000;33725000;42156000;50587000;59018000|30352000;40470000;50587000;60705000;70822000</t>
+  </si>
+  <si>
+    <t>20542000;27389000;34237000;41084000;47932000|25678000;34237000;42796000;51356000;59915000|30813000;41084000;51356000;61627000;71898000</t>
+  </si>
+  <si>
+    <t>20852000;27802000;34753000;41704000;48655000|26065000;34753000;43442000;52130000;60818000|31278000;41704000;52130000;62556000;72982000</t>
+  </si>
+  <si>
+    <t>21164000;28218000;35273000;42328000;49383000|26455000;35273000;44092000;52910000;61728000|31746000;42328000;52910000;63492000;74074000</t>
+  </si>
+  <si>
+    <t>21478000;28637000;35797000;42956000;50116000|26848000;35797000;44746000;53696000;62645000|32217000;42956000;53696000;64435000;75174000</t>
+  </si>
+  <si>
+    <t>21795000;29060000;36325000;43590000;50855000|27243000;36325000;45406000;54487000;63568000|32692000;43590000;54487000;65385000;76282000</t>
+  </si>
+  <si>
+    <t>22113000;29485000;36856000;44227000;51599000|27642000;36856000;46070000;55284000;64499000|33170000;44227000;55284000;66341000;77398000</t>
+  </si>
+  <si>
+    <t>23930000;31907000;39884000;47861000;55838000|29913000;39884000;49856000;59827000;69798000|35896000;47861000;59827000;71792000;83758000</t>
+  </si>
+  <si>
+    <t>24265000;32354000;40443000;48531000;56620000|30332000;40443000;50554000;60664000;70775000|36398000;48531000;60664000;72797000;84930000</t>
+  </si>
+  <si>
+    <t>24603000;32804000;41005000;49206000;57407000|30754000;41005000;51256000;61508000;71759000|36904000;49206000;61508000;73809000;86111000</t>
+  </si>
+  <si>
+    <t>24942000;33257000;41571000;49885000;58200000|31178000;41571000;51964000;62357000;72750000|37414000;49885000;62357000;74828000;87300000</t>
+  </si>
+  <si>
+    <t>25284000;33713000;42141000;50569000;58998000|31606000;42141000;52676000;63212000;73747000|37927000;50569000;63212000;75854000;88497000</t>
+  </si>
+  <si>
+    <t>25629000;34172000;42715000;51258000;59801000|32036000;42715000;53394000;64072000;74751000|38443000;51258000;64072000;76887000;89701000</t>
+  </si>
+  <si>
+    <t>25975000;34634000;43292000;51951000;60609000|32469000;43292000;54116000;64939000;75762000|38963000;51951000;64939000;77927000;90914000</t>
+  </si>
+  <si>
+    <t>26324000;35099000;43874000;52649000;61423000|32905000;43874000;54842000;65811000;76779000|39486000;52649000;65811000;78973000;92135000</t>
+  </si>
+  <si>
+    <t>26675000;35567000;44459000;53351000;62243000|33344000;44459000;55574000;66689000;77804000|40013000;53351000;66689000;80027000;93364000</t>
+  </si>
+  <si>
+    <t>27029000;36038000;45048000;54058000;63068000|33786000;45048000;56310000;67572000;78835000|40543000;54058000;67572000;81087000;94602000</t>
+  </si>
+  <si>
+    <t>28995000;38661000;48326000;57991000;67656000|36244000;48326000;60408000;72489000;84571000|43493000;57991000;72489000;86987000;101485000</t>
   </si>
 </sst>
 </file>
@@ -2003,13 +2003,13 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>220</v>
+        <v>129</v>
       </c>
       <c r="C3" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D3" t="s">
-        <v>216</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
         <v>116</v>
@@ -2023,13 +2023,13 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>221</v>
+        <v>130</v>
       </c>
       <c r="C4" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D4" t="s">
-        <v>217</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
         <v>117</v>
@@ -2043,13 +2043,13 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>222</v>
+        <v>131</v>
       </c>
       <c r="C5" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D5" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E5" t="s">
         <v>118</v>
@@ -2063,13 +2063,13 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>223</v>
+        <v>132</v>
       </c>
       <c r="C6" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D6" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E6" t="s">
         <v>119</v>
@@ -2083,13 +2083,13 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>224</v>
+        <v>133</v>
       </c>
       <c r="C7" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D7" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E7" t="s">
         <v>120</v>
@@ -2103,16 +2103,16 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>225</v>
+        <v>134</v>
       </c>
       <c r="C8" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D8" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E8" t="s">
-        <v>121</v>
+        <v>229</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
@@ -2123,16 +2123,16 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>226</v>
+        <v>135</v>
       </c>
       <c r="C9" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D9" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E9" t="s">
-        <v>122</v>
+        <v>230</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
@@ -2143,16 +2143,16 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>227</v>
+        <v>136</v>
       </c>
       <c r="C10" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D10" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E10" t="s">
-        <v>123</v>
+        <v>231</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
@@ -2163,16 +2163,16 @@
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>228</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D11" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E11" t="s">
-        <v>124</v>
+        <v>232</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
@@ -2183,16 +2183,16 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>229</v>
+        <v>138</v>
       </c>
       <c r="C12" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D12" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E12" t="s">
-        <v>125</v>
+        <v>233</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
@@ -2203,16 +2203,16 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>230</v>
+        <v>139</v>
       </c>
       <c r="C13" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D13" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E13" t="s">
-        <v>126</v>
+        <v>234</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
@@ -2223,16 +2223,16 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>231</v>
+        <v>140</v>
       </c>
       <c r="C14" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D14" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E14" t="s">
-        <v>127</v>
+        <v>235</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
@@ -2243,16 +2243,16 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>232</v>
+        <v>141</v>
       </c>
       <c r="C15" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D15" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E15" t="s">
-        <v>128</v>
+        <v>236</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
@@ -2263,16 +2263,16 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>233</v>
+        <v>142</v>
       </c>
       <c r="C16" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D16" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E16" t="s">
-        <v>129</v>
+        <v>237</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
@@ -2283,16 +2283,16 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>234</v>
+        <v>143</v>
       </c>
       <c r="C17" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D17" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E17" t="s">
-        <v>130</v>
+        <v>238</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
@@ -2303,16 +2303,16 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>235</v>
+        <v>144</v>
       </c>
       <c r="C18" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D18" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E18" t="s">
-        <v>131</v>
+        <v>239</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
@@ -2323,16 +2323,16 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>236</v>
+        <v>145</v>
       </c>
       <c r="C19" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D19" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E19" t="s">
-        <v>132</v>
+        <v>240</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
@@ -2343,16 +2343,16 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>237</v>
+        <v>146</v>
       </c>
       <c r="C20" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D20" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E20" t="s">
-        <v>133</v>
+        <v>241</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
@@ -2363,16 +2363,16 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>238</v>
+        <v>147</v>
       </c>
       <c r="C21" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D21" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E21" t="s">
-        <v>134</v>
+        <v>242</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
@@ -2383,16 +2383,16 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>239</v>
+        <v>148</v>
       </c>
       <c r="C22" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D22" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E22" t="s">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
@@ -2403,16 +2403,16 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>240</v>
+        <v>149</v>
       </c>
       <c r="C23" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D23" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E23" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="F23" t="s">
         <v>34</v>
@@ -2423,16 +2423,16 @@
         <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>241</v>
+        <v>150</v>
       </c>
       <c r="C24" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D24" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E24" t="s">
-        <v>137</v>
+        <v>244</v>
       </c>
       <c r="F24" t="s">
         <v>34</v>
@@ -2443,16 +2443,16 @@
         <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>242</v>
+        <v>151</v>
       </c>
       <c r="C25" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D25" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E25" t="s">
-        <v>138</v>
+        <v>245</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -2463,16 +2463,16 @@
         <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>243</v>
+        <v>152</v>
       </c>
       <c r="C26" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D26" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E26" t="s">
-        <v>139</v>
+        <v>246</v>
       </c>
       <c r="F26" t="s">
         <v>34</v>
@@ -2483,16 +2483,16 @@
         <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>244</v>
+        <v>153</v>
       </c>
       <c r="C27" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D27" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E27" t="s">
-        <v>140</v>
+        <v>247</v>
       </c>
       <c r="F27" t="s">
         <v>34</v>
@@ -2503,16 +2503,16 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>245</v>
+        <v>154</v>
       </c>
       <c r="C28" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D28" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E28" t="s">
-        <v>141</v>
+        <v>248</v>
       </c>
       <c r="F28" t="s">
         <v>34</v>
@@ -2523,16 +2523,16 @@
         <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>246</v>
+        <v>155</v>
       </c>
       <c r="C29" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D29" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E29" t="s">
-        <v>142</v>
+        <v>249</v>
       </c>
       <c r="F29" t="s">
         <v>34</v>
@@ -2543,16 +2543,16 @@
         <v>41</v>
       </c>
       <c r="B30" t="s">
-        <v>247</v>
+        <v>156</v>
       </c>
       <c r="C30" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D30" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E30" t="s">
-        <v>143</v>
+        <v>250</v>
       </c>
       <c r="F30" t="s">
         <v>34</v>
@@ -2563,16 +2563,16 @@
         <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>248</v>
+        <v>157</v>
       </c>
       <c r="C31" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D31" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E31" t="s">
-        <v>144</v>
+        <v>251</v>
       </c>
       <c r="F31" t="s">
         <v>34</v>
@@ -2583,16 +2583,16 @@
         <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>249</v>
+        <v>158</v>
       </c>
       <c r="C32" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D32" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E32" t="s">
-        <v>145</v>
+        <v>252</v>
       </c>
       <c r="F32" t="s">
         <v>34</v>
@@ -2603,16 +2603,16 @@
         <v>44</v>
       </c>
       <c r="B33" t="s">
-        <v>250</v>
+        <v>159</v>
       </c>
       <c r="C33" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D33" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E33" t="s">
-        <v>146</v>
+        <v>253</v>
       </c>
       <c r="F33" t="s">
         <v>34</v>
@@ -2623,16 +2623,16 @@
         <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>251</v>
+        <v>160</v>
       </c>
       <c r="C34" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D34" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E34" t="s">
-        <v>147</v>
+        <v>254</v>
       </c>
       <c r="F34" t="s">
         <v>34</v>
@@ -2643,16 +2643,16 @@
         <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>252</v>
+        <v>161</v>
       </c>
       <c r="C35" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D35" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E35" t="s">
-        <v>148</v>
+        <v>255</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -2663,16 +2663,16 @@
         <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>253</v>
+        <v>162</v>
       </c>
       <c r="C36" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D36" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E36" t="s">
-        <v>149</v>
+        <v>256</v>
       </c>
       <c r="F36" t="s">
         <v>34</v>
@@ -2683,16 +2683,16 @@
         <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>254</v>
+        <v>163</v>
       </c>
       <c r="C37" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D37" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E37" t="s">
-        <v>150</v>
+        <v>257</v>
       </c>
       <c r="F37" t="s">
         <v>34</v>
@@ -2703,16 +2703,16 @@
         <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>255</v>
+        <v>164</v>
       </c>
       <c r="C38" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D38" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E38" t="s">
-        <v>151</v>
+        <v>258</v>
       </c>
       <c r="F38" t="s">
         <v>34</v>
@@ -2723,16 +2723,16 @@
         <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>256</v>
+        <v>165</v>
       </c>
       <c r="C39" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D39" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E39" t="s">
-        <v>152</v>
+        <v>259</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
@@ -2743,16 +2743,16 @@
         <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>257</v>
+        <v>166</v>
       </c>
       <c r="C40" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D40" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E40" t="s">
-        <v>153</v>
+        <v>260</v>
       </c>
       <c r="F40" t="s">
         <v>34</v>
@@ -2763,16 +2763,16 @@
         <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>258</v>
+        <v>167</v>
       </c>
       <c r="C41" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D41" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E41" t="s">
-        <v>154</v>
+        <v>261</v>
       </c>
       <c r="F41" t="s">
         <v>34</v>
@@ -2783,16 +2783,16 @@
         <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>259</v>
+        <v>168</v>
       </c>
       <c r="C42" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D42" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E42" t="s">
-        <v>155</v>
+        <v>262</v>
       </c>
       <c r="F42" t="s">
         <v>34</v>
@@ -2803,16 +2803,16 @@
         <v>54</v>
       </c>
       <c r="B43" t="s">
-        <v>260</v>
+        <v>169</v>
       </c>
       <c r="C43" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D43" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E43" t="s">
-        <v>156</v>
+        <v>263</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
@@ -2823,16 +2823,16 @@
         <v>55</v>
       </c>
       <c r="B44" t="s">
-        <v>261</v>
+        <v>170</v>
       </c>
       <c r="C44" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D44" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E44" t="s">
-        <v>157</v>
+        <v>264</v>
       </c>
       <c r="F44" t="s">
         <v>34</v>
@@ -2843,16 +2843,16 @@
         <v>56</v>
       </c>
       <c r="B45" t="s">
-        <v>262</v>
+        <v>171</v>
       </c>
       <c r="C45" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D45" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E45" t="s">
-        <v>158</v>
+        <v>265</v>
       </c>
       <c r="F45" t="s">
         <v>34</v>
@@ -2863,16 +2863,16 @@
         <v>57</v>
       </c>
       <c r="B46" t="s">
-        <v>263</v>
+        <v>172</v>
       </c>
       <c r="C46" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D46" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E46" t="s">
-        <v>159</v>
+        <v>266</v>
       </c>
       <c r="F46" t="s">
         <v>34</v>
@@ -2883,16 +2883,16 @@
         <v>58</v>
       </c>
       <c r="B47" t="s">
-        <v>264</v>
+        <v>173</v>
       </c>
       <c r="C47" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D47" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E47" t="s">
-        <v>160</v>
+        <v>267</v>
       </c>
       <c r="F47" t="s">
         <v>34</v>
@@ -2903,16 +2903,16 @@
         <v>59</v>
       </c>
       <c r="B48" t="s">
-        <v>265</v>
+        <v>174</v>
       </c>
       <c r="C48" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D48" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E48" t="s">
-        <v>161</v>
+        <v>268</v>
       </c>
       <c r="F48" t="s">
         <v>34</v>
@@ -2923,16 +2923,16 @@
         <v>60</v>
       </c>
       <c r="B49" t="s">
-        <v>266</v>
+        <v>175</v>
       </c>
       <c r="C49" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D49" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E49" t="s">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="F49" t="s">
         <v>34</v>
@@ -2943,16 +2943,16 @@
         <v>61</v>
       </c>
       <c r="B50" t="s">
-        <v>267</v>
+        <v>176</v>
       </c>
       <c r="C50" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D50" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E50" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="F50" t="s">
         <v>34</v>
@@ -2963,16 +2963,16 @@
         <v>62</v>
       </c>
       <c r="B51" t="s">
-        <v>268</v>
+        <v>177</v>
       </c>
       <c r="C51" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D51" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E51" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
@@ -2983,16 +2983,16 @@
         <v>63</v>
       </c>
       <c r="B52" t="s">
-        <v>269</v>
+        <v>178</v>
       </c>
       <c r="C52" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D52" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E52" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F52" t="s">
         <v>34</v>
@@ -3003,16 +3003,16 @@
         <v>64</v>
       </c>
       <c r="B53" t="s">
-        <v>270</v>
+        <v>179</v>
       </c>
       <c r="C53" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D53" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E53" t="s">
-        <v>166</v>
+        <v>272</v>
       </c>
       <c r="F53" t="s">
         <v>65</v>
@@ -3023,16 +3023,16 @@
         <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>271</v>
+        <v>180</v>
       </c>
       <c r="C54" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D54" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E54" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="F54" t="s">
         <v>65</v>
@@ -3043,16 +3043,16 @@
         <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>272</v>
+        <v>181</v>
       </c>
       <c r="C55" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D55" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E55" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="F55" t="s">
         <v>65</v>
@@ -3063,16 +3063,16 @@
         <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>273</v>
+        <v>182</v>
       </c>
       <c r="C56" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D56" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E56" t="s">
-        <v>169</v>
+        <v>275</v>
       </c>
       <c r="F56" t="s">
         <v>65</v>
@@ -3083,16 +3083,16 @@
         <v>69</v>
       </c>
       <c r="B57" t="s">
-        <v>274</v>
+        <v>183</v>
       </c>
       <c r="C57" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D57" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E57" t="s">
-        <v>170</v>
+        <v>276</v>
       </c>
       <c r="F57" t="s">
         <v>65</v>
@@ -3103,16 +3103,16 @@
         <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>275</v>
+        <v>184</v>
       </c>
       <c r="C58" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D58" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E58" t="s">
-        <v>171</v>
+        <v>277</v>
       </c>
       <c r="F58" t="s">
         <v>65</v>
@@ -3123,16 +3123,16 @@
         <v>71</v>
       </c>
       <c r="B59" t="s">
-        <v>276</v>
+        <v>185</v>
       </c>
       <c r="C59" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D59" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E59" t="s">
-        <v>172</v>
+        <v>278</v>
       </c>
       <c r="F59" t="s">
         <v>65</v>
@@ -3143,16 +3143,16 @@
         <v>72</v>
       </c>
       <c r="B60" t="s">
-        <v>277</v>
+        <v>186</v>
       </c>
       <c r="C60" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D60" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E60" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="F60" t="s">
         <v>65</v>
@@ -3163,16 +3163,16 @@
         <v>73</v>
       </c>
       <c r="B61" t="s">
-        <v>278</v>
+        <v>187</v>
       </c>
       <c r="C61" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D61" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E61" t="s">
-        <v>174</v>
+        <v>280</v>
       </c>
       <c r="F61" t="s">
         <v>65</v>
@@ -3183,16 +3183,16 @@
         <v>74</v>
       </c>
       <c r="B62" t="s">
-        <v>279</v>
+        <v>188</v>
       </c>
       <c r="C62" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D62" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E62" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="F62" t="s">
         <v>65</v>
@@ -3203,16 +3203,16 @@
         <v>75</v>
       </c>
       <c r="B63" t="s">
-        <v>280</v>
+        <v>189</v>
       </c>
       <c r="C63" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D63" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E63" t="s">
-        <v>176</v>
+        <v>281</v>
       </c>
       <c r="F63" t="s">
         <v>65</v>
@@ -3223,16 +3223,16 @@
         <v>76</v>
       </c>
       <c r="B64" t="s">
-        <v>281</v>
+        <v>190</v>
       </c>
       <c r="C64" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D64" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E64" t="s">
-        <v>177</v>
+        <v>282</v>
       </c>
       <c r="F64" t="s">
         <v>65</v>
@@ -3243,16 +3243,16 @@
         <v>77</v>
       </c>
       <c r="B65" t="s">
-        <v>282</v>
+        <v>191</v>
       </c>
       <c r="C65" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D65" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E65" t="s">
-        <v>178</v>
+        <v>283</v>
       </c>
       <c r="F65" t="s">
         <v>65</v>
@@ -3263,16 +3263,16 @@
         <v>78</v>
       </c>
       <c r="B66" t="s">
-        <v>283</v>
+        <v>192</v>
       </c>
       <c r="C66" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D66" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E66" t="s">
-        <v>179</v>
+        <v>284</v>
       </c>
       <c r="F66" t="s">
         <v>65</v>
@@ -3283,16 +3283,16 @@
         <v>79</v>
       </c>
       <c r="B67" t="s">
-        <v>284</v>
+        <v>193</v>
       </c>
       <c r="C67" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D67" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E67" t="s">
-        <v>180</v>
+        <v>285</v>
       </c>
       <c r="F67" t="s">
         <v>65</v>
@@ -3303,16 +3303,16 @@
         <v>80</v>
       </c>
       <c r="B68" t="s">
-        <v>285</v>
+        <v>194</v>
       </c>
       <c r="C68" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D68" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E68" t="s">
-        <v>181</v>
+        <v>286</v>
       </c>
       <c r="F68" t="s">
         <v>65</v>
@@ -3323,16 +3323,16 @@
         <v>81</v>
       </c>
       <c r="B69" t="s">
-        <v>286</v>
+        <v>195</v>
       </c>
       <c r="C69" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D69" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E69" t="s">
-        <v>182</v>
+        <v>287</v>
       </c>
       <c r="F69" t="s">
         <v>65</v>
@@ -3343,16 +3343,16 @@
         <v>82</v>
       </c>
       <c r="B70" t="s">
-        <v>287</v>
+        <v>196</v>
       </c>
       <c r="C70" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D70" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E70" t="s">
-        <v>183</v>
+        <v>288</v>
       </c>
       <c r="F70" t="s">
         <v>65</v>
@@ -3363,16 +3363,16 @@
         <v>83</v>
       </c>
       <c r="B71" t="s">
-        <v>288</v>
+        <v>197</v>
       </c>
       <c r="C71" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D71" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E71" t="s">
-        <v>184</v>
+        <v>289</v>
       </c>
       <c r="F71" t="s">
         <v>65</v>
@@ -3383,16 +3383,16 @@
         <v>84</v>
       </c>
       <c r="B72" t="s">
-        <v>289</v>
+        <v>198</v>
       </c>
       <c r="C72" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D72" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E72" t="s">
-        <v>185</v>
+        <v>290</v>
       </c>
       <c r="F72" t="s">
         <v>65</v>
@@ -3403,16 +3403,16 @@
         <v>85</v>
       </c>
       <c r="B73" t="s">
-        <v>290</v>
+        <v>199</v>
       </c>
       <c r="C73" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D73" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E73" t="s">
-        <v>186</v>
+        <v>291</v>
       </c>
       <c r="F73" t="s">
         <v>65</v>
@@ -3423,16 +3423,16 @@
         <v>86</v>
       </c>
       <c r="B74" t="s">
-        <v>291</v>
+        <v>200</v>
       </c>
       <c r="C74" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D74" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E74" t="s">
-        <v>187</v>
+        <v>292</v>
       </c>
       <c r="F74" t="s">
         <v>65</v>
@@ -3443,16 +3443,16 @@
         <v>87</v>
       </c>
       <c r="B75" t="s">
-        <v>292</v>
+        <v>201</v>
       </c>
       <c r="C75" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D75" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E75" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="F75" t="s">
         <v>65</v>
@@ -3463,16 +3463,16 @@
         <v>88</v>
       </c>
       <c r="B76" t="s">
-        <v>293</v>
+        <v>202</v>
       </c>
       <c r="C76" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D76" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E76" t="s">
-        <v>189</v>
+        <v>294</v>
       </c>
       <c r="F76" t="s">
         <v>65</v>
@@ -3483,16 +3483,16 @@
         <v>89</v>
       </c>
       <c r="B77" t="s">
-        <v>294</v>
+        <v>203</v>
       </c>
       <c r="C77" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D77" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="E77" t="s">
-        <v>190</v>
+        <v>124</v>
       </c>
       <c r="F77" t="s">
         <v>65</v>
@@ -3503,16 +3503,16 @@
         <v>90</v>
       </c>
       <c r="B78" t="s">
+        <v>204</v>
+      </c>
+      <c r="C78" t="s">
+        <v>128</v>
+      </c>
+      <c r="D78" t="s">
+        <v>127</v>
+      </c>
+      <c r="E78" t="s">
         <v>295</v>
-      </c>
-      <c r="C78" t="s">
-        <v>219</v>
-      </c>
-      <c r="D78" t="s">
-        <v>218</v>
-      </c>
-      <c r="E78" t="s">
-        <v>191</v>
       </c>
       <c r="F78" t="s">
         <v>65</v>
@@ -3523,16 +3523,16 @@
         <v>91</v>
       </c>
       <c r="B79" t="s">
+        <v>205</v>
+      </c>
+      <c r="C79" t="s">
+        <v>128</v>
+      </c>
+      <c r="D79" t="s">
+        <v>127</v>
+      </c>
+      <c r="E79" t="s">
         <v>296</v>
-      </c>
-      <c r="C79" t="s">
-        <v>219</v>
-      </c>
-      <c r="D79" t="s">
-        <v>218</v>
-      </c>
-      <c r="E79" t="s">
-        <v>192</v>
       </c>
       <c r="F79" t="s">
         <v>65</v>
@@ -3543,16 +3543,16 @@
         <v>92</v>
       </c>
       <c r="B80" t="s">
+        <v>206</v>
+      </c>
+      <c r="C80" t="s">
+        <v>128</v>
+      </c>
+      <c r="D80" t="s">
+        <v>127</v>
+      </c>
+      <c r="E80" t="s">
         <v>297</v>
-      </c>
-      <c r="C80" t="s">
-        <v>219</v>
-      </c>
-      <c r="D80" t="s">
-        <v>218</v>
-      </c>
-      <c r="E80" t="s">
-        <v>193</v>
       </c>
       <c r="F80" t="s">
         <v>65</v>
@@ -3563,16 +3563,16 @@
         <v>93</v>
       </c>
       <c r="B81" t="s">
+        <v>207</v>
+      </c>
+      <c r="C81" t="s">
+        <v>128</v>
+      </c>
+      <c r="D81" t="s">
+        <v>127</v>
+      </c>
+      <c r="E81" t="s">
         <v>298</v>
-      </c>
-      <c r="C81" t="s">
-        <v>219</v>
-      </c>
-      <c r="D81" t="s">
-        <v>218</v>
-      </c>
-      <c r="E81" t="s">
-        <v>194</v>
       </c>
       <c r="F81" t="s">
         <v>65</v>
@@ -3583,16 +3583,16 @@
         <v>94</v>
       </c>
       <c r="B82" t="s">
+        <v>208</v>
+      </c>
+      <c r="C82" t="s">
+        <v>128</v>
+      </c>
+      <c r="D82" t="s">
+        <v>127</v>
+      </c>
+      <c r="E82" t="s">
         <v>299</v>
-      </c>
-      <c r="C82" t="s">
-        <v>219</v>
-      </c>
-      <c r="D82" t="s">
-        <v>218</v>
-      </c>
-      <c r="E82" t="s">
-        <v>195</v>
       </c>
       <c r="F82" t="s">
         <v>65</v>
@@ -3603,16 +3603,16 @@
         <v>95</v>
       </c>
       <c r="B83" t="s">
+        <v>209</v>
+      </c>
+      <c r="C83" t="s">
+        <v>128</v>
+      </c>
+      <c r="D83" t="s">
+        <v>127</v>
+      </c>
+      <c r="E83" t="s">
         <v>300</v>
-      </c>
-      <c r="C83" t="s">
-        <v>219</v>
-      </c>
-      <c r="D83" t="s">
-        <v>218</v>
-      </c>
-      <c r="E83" t="s">
-        <v>196</v>
       </c>
       <c r="F83" t="s">
         <v>96</v>
@@ -3623,16 +3623,16 @@
         <v>97</v>
       </c>
       <c r="B84" t="s">
+        <v>210</v>
+      </c>
+      <c r="C84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D84" t="s">
+        <v>127</v>
+      </c>
+      <c r="E84" t="s">
         <v>301</v>
-      </c>
-      <c r="C84" t="s">
-        <v>219</v>
-      </c>
-      <c r="D84" t="s">
-        <v>218</v>
-      </c>
-      <c r="E84" t="s">
-        <v>197</v>
       </c>
       <c r="F84" t="s">
         <v>96</v>
@@ -3643,16 +3643,16 @@
         <v>98</v>
       </c>
       <c r="B85" t="s">
+        <v>211</v>
+      </c>
+      <c r="C85" t="s">
+        <v>128</v>
+      </c>
+      <c r="D85" t="s">
+        <v>127</v>
+      </c>
+      <c r="E85" t="s">
         <v>302</v>
-      </c>
-      <c r="C85" t="s">
-        <v>219</v>
-      </c>
-      <c r="D85" t="s">
-        <v>218</v>
-      </c>
-      <c r="E85" t="s">
-        <v>198</v>
       </c>
       <c r="F85" t="s">
         <v>96</v>
@@ -3663,16 +3663,16 @@
         <v>99</v>
       </c>
       <c r="B86" t="s">
+        <v>212</v>
+      </c>
+      <c r="C86" t="s">
+        <v>128</v>
+      </c>
+      <c r="D86" t="s">
+        <v>127</v>
+      </c>
+      <c r="E86" t="s">
         <v>303</v>
-      </c>
-      <c r="C86" t="s">
-        <v>219</v>
-      </c>
-      <c r="D86" t="s">
-        <v>218</v>
-      </c>
-      <c r="E86" t="s">
-        <v>199</v>
       </c>
       <c r="F86" t="s">
         <v>96</v>
@@ -3683,16 +3683,16 @@
         <v>100</v>
       </c>
       <c r="B87" t="s">
+        <v>213</v>
+      </c>
+      <c r="C87" t="s">
+        <v>128</v>
+      </c>
+      <c r="D87" t="s">
+        <v>127</v>
+      </c>
+      <c r="E87" t="s">
         <v>304</v>
-      </c>
-      <c r="C87" t="s">
-        <v>219</v>
-      </c>
-      <c r="D87" t="s">
-        <v>218</v>
-      </c>
-      <c r="E87" t="s">
-        <v>200</v>
       </c>
       <c r="F87" t="s">
         <v>96</v>
@@ -3703,16 +3703,16 @@
         <v>101</v>
       </c>
       <c r="B88" t="s">
+        <v>214</v>
+      </c>
+      <c r="C88" t="s">
+        <v>128</v>
+      </c>
+      <c r="D88" t="s">
+        <v>127</v>
+      </c>
+      <c r="E88" t="s">
         <v>305</v>
-      </c>
-      <c r="C88" t="s">
-        <v>219</v>
-      </c>
-      <c r="D88" t="s">
-        <v>218</v>
-      </c>
-      <c r="E88" t="s">
-        <v>201</v>
       </c>
       <c r="F88" t="s">
         <v>96</v>
@@ -3723,16 +3723,16 @@
         <v>102</v>
       </c>
       <c r="B89" t="s">
+        <v>215</v>
+      </c>
+      <c r="C89" t="s">
+        <v>128</v>
+      </c>
+      <c r="D89" t="s">
+        <v>127</v>
+      </c>
+      <c r="E89" t="s">
         <v>306</v>
-      </c>
-      <c r="C89" t="s">
-        <v>219</v>
-      </c>
-      <c r="D89" t="s">
-        <v>218</v>
-      </c>
-      <c r="E89" t="s">
-        <v>202</v>
       </c>
       <c r="F89" t="s">
         <v>96</v>
@@ -3743,16 +3743,16 @@
         <v>103</v>
       </c>
       <c r="B90" t="s">
+        <v>216</v>
+      </c>
+      <c r="C90" t="s">
+        <v>128</v>
+      </c>
+      <c r="D90" t="s">
+        <v>127</v>
+      </c>
+      <c r="E90" t="s">
         <v>307</v>
-      </c>
-      <c r="C90" t="s">
-        <v>219</v>
-      </c>
-      <c r="D90" t="s">
-        <v>218</v>
-      </c>
-      <c r="E90" t="s">
-        <v>203</v>
       </c>
       <c r="F90" t="s">
         <v>96</v>
@@ -3763,16 +3763,16 @@
         <v>104</v>
       </c>
       <c r="B91" t="s">
+        <v>217</v>
+      </c>
+      <c r="C91" t="s">
+        <v>128</v>
+      </c>
+      <c r="D91" t="s">
+        <v>127</v>
+      </c>
+      <c r="E91" t="s">
         <v>308</v>
-      </c>
-      <c r="C91" t="s">
-        <v>219</v>
-      </c>
-      <c r="D91" t="s">
-        <v>218</v>
-      </c>
-      <c r="E91" t="s">
-        <v>204</v>
       </c>
       <c r="F91" t="s">
         <v>96</v>
@@ -3783,16 +3783,16 @@
         <v>105</v>
       </c>
       <c r="B92" t="s">
+        <v>218</v>
+      </c>
+      <c r="C92" t="s">
+        <v>128</v>
+      </c>
+      <c r="D92" t="s">
+        <v>127</v>
+      </c>
+      <c r="E92" t="s">
         <v>309</v>
-      </c>
-      <c r="C92" t="s">
-        <v>219</v>
-      </c>
-      <c r="D92" t="s">
-        <v>218</v>
-      </c>
-      <c r="E92" t="s">
-        <v>205</v>
       </c>
       <c r="F92" t="s">
         <v>96</v>
@@ -3803,16 +3803,16 @@
         <v>106</v>
       </c>
       <c r="B93" t="s">
+        <v>219</v>
+      </c>
+      <c r="C93" t="s">
+        <v>128</v>
+      </c>
+      <c r="D93" t="s">
+        <v>127</v>
+      </c>
+      <c r="E93" t="s">
         <v>310</v>
-      </c>
-      <c r="C93" t="s">
-        <v>219</v>
-      </c>
-      <c r="D93" t="s">
-        <v>218</v>
-      </c>
-      <c r="E93" t="s">
-        <v>206</v>
       </c>
       <c r="F93" t="s">
         <v>96</v>
@@ -3823,16 +3823,16 @@
         <v>107</v>
       </c>
       <c r="B94" t="s">
+        <v>220</v>
+      </c>
+      <c r="C94" t="s">
+        <v>128</v>
+      </c>
+      <c r="D94" t="s">
+        <v>127</v>
+      </c>
+      <c r="E94" t="s">
         <v>311</v>
-      </c>
-      <c r="C94" t="s">
-        <v>219</v>
-      </c>
-      <c r="D94" t="s">
-        <v>218</v>
-      </c>
-      <c r="E94" t="s">
-        <v>207</v>
       </c>
       <c r="F94" t="s">
         <v>96</v>
@@ -3843,16 +3843,16 @@
         <v>108</v>
       </c>
       <c r="B95" t="s">
+        <v>221</v>
+      </c>
+      <c r="C95" t="s">
+        <v>128</v>
+      </c>
+      <c r="D95" t="s">
+        <v>127</v>
+      </c>
+      <c r="E95" t="s">
         <v>312</v>
-      </c>
-      <c r="C95" t="s">
-        <v>219</v>
-      </c>
-      <c r="D95" t="s">
-        <v>218</v>
-      </c>
-      <c r="E95" t="s">
-        <v>208</v>
       </c>
       <c r="F95" t="s">
         <v>96</v>
@@ -3863,16 +3863,16 @@
         <v>109</v>
       </c>
       <c r="B96" t="s">
+        <v>222</v>
+      </c>
+      <c r="C96" t="s">
+        <v>128</v>
+      </c>
+      <c r="D96" t="s">
+        <v>127</v>
+      </c>
+      <c r="E96" t="s">
         <v>313</v>
-      </c>
-      <c r="C96" t="s">
-        <v>219</v>
-      </c>
-      <c r="D96" t="s">
-        <v>218</v>
-      </c>
-      <c r="E96" t="s">
-        <v>209</v>
       </c>
       <c r="F96" t="s">
         <v>96</v>
@@ -3883,16 +3883,16 @@
         <v>110</v>
       </c>
       <c r="B97" t="s">
+        <v>223</v>
+      </c>
+      <c r="C97" t="s">
+        <v>128</v>
+      </c>
+      <c r="D97" t="s">
+        <v>127</v>
+      </c>
+      <c r="E97" t="s">
         <v>314</v>
-      </c>
-      <c r="C97" t="s">
-        <v>219</v>
-      </c>
-      <c r="D97" t="s">
-        <v>218</v>
-      </c>
-      <c r="E97" t="s">
-        <v>210</v>
       </c>
       <c r="F97" t="s">
         <v>96</v>
@@ -3903,16 +3903,16 @@
         <v>111</v>
       </c>
       <c r="B98" t="s">
+        <v>224</v>
+      </c>
+      <c r="C98" t="s">
+        <v>128</v>
+      </c>
+      <c r="D98" t="s">
+        <v>127</v>
+      </c>
+      <c r="E98" t="s">
         <v>315</v>
-      </c>
-      <c r="C98" t="s">
-        <v>219</v>
-      </c>
-      <c r="D98" t="s">
-        <v>218</v>
-      </c>
-      <c r="E98" t="s">
-        <v>211</v>
       </c>
       <c r="F98" t="s">
         <v>96</v>
@@ -3923,16 +3923,16 @@
         <v>112</v>
       </c>
       <c r="B99" t="s">
+        <v>225</v>
+      </c>
+      <c r="C99" t="s">
+        <v>128</v>
+      </c>
+      <c r="D99" t="s">
+        <v>127</v>
+      </c>
+      <c r="E99" t="s">
         <v>316</v>
-      </c>
-      <c r="C99" t="s">
-        <v>219</v>
-      </c>
-      <c r="D99" t="s">
-        <v>218</v>
-      </c>
-      <c r="E99" t="s">
-        <v>212</v>
       </c>
       <c r="F99" t="s">
         <v>96</v>
@@ -3943,16 +3943,16 @@
         <v>113</v>
       </c>
       <c r="B100" t="s">
+        <v>226</v>
+      </c>
+      <c r="C100" t="s">
+        <v>128</v>
+      </c>
+      <c r="D100" t="s">
+        <v>127</v>
+      </c>
+      <c r="E100" t="s">
         <v>317</v>
-      </c>
-      <c r="C100" t="s">
-        <v>219</v>
-      </c>
-      <c r="D100" t="s">
-        <v>218</v>
-      </c>
-      <c r="E100" t="s">
-        <v>213</v>
       </c>
       <c r="F100" t="s">
         <v>96</v>
@@ -3963,16 +3963,16 @@
         <v>114</v>
       </c>
       <c r="B101" t="s">
+        <v>227</v>
+      </c>
+      <c r="C101" t="s">
+        <v>128</v>
+      </c>
+      <c r="D101" t="s">
+        <v>127</v>
+      </c>
+      <c r="E101" t="s">
         <v>318</v>
-      </c>
-      <c r="C101" t="s">
-        <v>219</v>
-      </c>
-      <c r="D101" t="s">
-        <v>218</v>
-      </c>
-      <c r="E101" t="s">
-        <v>214</v>
       </c>
       <c r="F101" t="s">
         <v>96</v>
@@ -3983,16 +3983,16 @@
         <v>115</v>
       </c>
       <c r="B102" t="s">
+        <v>228</v>
+      </c>
+      <c r="C102" t="s">
+        <v>128</v>
+      </c>
+      <c r="D102" t="s">
+        <v>127</v>
+      </c>
+      <c r="E102" t="s">
         <v>319</v>
-      </c>
-      <c r="C102" t="s">
-        <v>219</v>
-      </c>
-      <c r="D102" t="s">
-        <v>218</v>
-      </c>
-      <c r="E102" t="s">
-        <v>215</v>
       </c>
       <c r="F102" t="s">
         <v>96</v>

--- a/Assets/Config/Holmas_AgencyBuildingTable.xlsx
+++ b/Assets/Config/Holmas_AgencyBuildingTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Holmas\Assets\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29CBDAB-4BAD-4E45-8DC5-BAA77F6E8A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D15D30-FF41-4871-BFEF-278F578CF36D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="332">
   <si>
     <t>城市阶段id</t>
   </si>
@@ -998,6 +998,45 @@
   </si>
   <si>
     <t>28995000;38661000;48326000;57991000;67656000|36244000;48326000;60408000;72489000;84571000|43493000;57991000;72489000;86987000;101485000</t>
+  </si>
+  <si>
+    <t>城市图片</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>stageImage</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Textures/buildings/building01.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Textures/buildings/building02.png</t>
+  </si>
+  <si>
+    <t>Textures/buildings/building03.png</t>
+  </si>
+  <si>
+    <t>Textures/buildings/building04.png</t>
+  </si>
+  <si>
+    <t>Textures/buildings/building05.png</t>
+  </si>
+  <si>
+    <t>Textures/buildings/building06.png</t>
+  </si>
+  <si>
+    <t>Textures/buildings/building07.png</t>
+  </si>
+  <si>
+    <t>Textures/buildings/building08.png</t>
+  </si>
+  <si>
+    <t>Textures/buildings/building09.png</t>
+  </si>
+  <si>
+    <t>Textures/buildings/building10.png</t>
   </si>
 </sst>
 </file>
@@ -1949,16 +1988,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="73.4140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="73.4140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1966,19 +2006,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1986,19 +2029,22 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2006,19 +2052,22 @@
         <v>129</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>322</v>
       </c>
       <c r="D3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" t="s">
         <v>125</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>116</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -2026,19 +2075,22 @@
         <v>130</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>323</v>
       </c>
       <c r="D4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" t="s">
         <v>126</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>117</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -2046,19 +2098,22 @@
         <v>131</v>
       </c>
       <c r="C5" t="s">
-        <v>128</v>
+        <v>324</v>
       </c>
       <c r="D5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F5" t="s">
         <v>118</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -2066,19 +2121,22 @@
         <v>132</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>325</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F6" t="s">
         <v>119</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -2086,19 +2144,22 @@
         <v>133</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
+        <v>326</v>
       </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F7" t="s">
         <v>120</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -2106,19 +2167,22 @@
         <v>134</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>327</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8" t="s">
         <v>229</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -2126,19 +2190,22 @@
         <v>135</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>328</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E9" t="s">
+        <v>127</v>
+      </c>
+      <c r="F9" t="s">
         <v>230</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -2146,19 +2213,22 @@
         <v>136</v>
       </c>
       <c r="C10" t="s">
-        <v>128</v>
+        <v>329</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F10" t="s">
         <v>231</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -2166,19 +2236,22 @@
         <v>137</v>
       </c>
       <c r="C11" t="s">
-        <v>128</v>
+        <v>330</v>
       </c>
       <c r="D11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" t="s">
         <v>232</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -2186,19 +2259,22 @@
         <v>138</v>
       </c>
       <c r="C12" t="s">
-        <v>128</v>
+        <v>331</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E12" t="s">
+        <v>127</v>
+      </c>
+      <c r="F12" t="s">
         <v>233</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -2206,19 +2282,22 @@
         <v>139</v>
       </c>
       <c r="C13" t="s">
-        <v>128</v>
+        <v>322</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E13" t="s">
+        <v>127</v>
+      </c>
+      <c r="F13" t="s">
         <v>234</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -2226,19 +2305,22 @@
         <v>140</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>323</v>
       </c>
       <c r="D14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E14" t="s">
+        <v>127</v>
+      </c>
+      <c r="F14" t="s">
         <v>235</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -2246,19 +2328,22 @@
         <v>141</v>
       </c>
       <c r="C15" t="s">
-        <v>128</v>
+        <v>324</v>
       </c>
       <c r="D15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E15" t="s">
+        <v>127</v>
+      </c>
+      <c r="F15" t="s">
         <v>236</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -2266,19 +2351,22 @@
         <v>142</v>
       </c>
       <c r="C16" t="s">
-        <v>128</v>
+        <v>325</v>
       </c>
       <c r="D16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E16" t="s">
+        <v>127</v>
+      </c>
+      <c r="F16" t="s">
         <v>237</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -2286,19 +2374,22 @@
         <v>143</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
+        <v>326</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E17" t="s">
+        <v>127</v>
+      </c>
+      <c r="F17" t="s">
         <v>238</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -2306,19 +2397,22 @@
         <v>144</v>
       </c>
       <c r="C18" t="s">
-        <v>128</v>
+        <v>327</v>
       </c>
       <c r="D18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E18" t="s">
+        <v>127</v>
+      </c>
+      <c r="F18" t="s">
         <v>239</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -2326,19 +2420,22 @@
         <v>145</v>
       </c>
       <c r="C19" t="s">
-        <v>128</v>
+        <v>328</v>
       </c>
       <c r="D19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E19" t="s">
+        <v>127</v>
+      </c>
+      <c r="F19" t="s">
         <v>240</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -2346,19 +2443,22 @@
         <v>146</v>
       </c>
       <c r="C20" t="s">
-        <v>128</v>
+        <v>329</v>
       </c>
       <c r="D20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E20" t="s">
+        <v>127</v>
+      </c>
+      <c r="F20" t="s">
         <v>241</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -2366,19 +2466,22 @@
         <v>147</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>330</v>
       </c>
       <c r="D21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E21" t="s">
+        <v>127</v>
+      </c>
+      <c r="F21" t="s">
         <v>242</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>32</v>
       </c>
@@ -2386,19 +2489,22 @@
         <v>148</v>
       </c>
       <c r="C22" t="s">
-        <v>128</v>
+        <v>331</v>
       </c>
       <c r="D22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E22" t="s">
+        <v>127</v>
+      </c>
+      <c r="F22" t="s">
         <v>243</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -2406,19 +2512,22 @@
         <v>149</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>322</v>
       </c>
       <c r="D23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E23" t="s">
+        <v>127</v>
+      </c>
+      <c r="F23" t="s">
         <v>121</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -2426,19 +2535,22 @@
         <v>150</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>323</v>
       </c>
       <c r="D24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E24" t="s">
+        <v>127</v>
+      </c>
+      <c r="F24" t="s">
         <v>244</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -2446,19 +2558,22 @@
         <v>151</v>
       </c>
       <c r="C25" t="s">
-        <v>128</v>
+        <v>324</v>
       </c>
       <c r="D25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E25" t="s">
+        <v>127</v>
+      </c>
+      <c r="F25" t="s">
         <v>245</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -2466,19 +2581,22 @@
         <v>152</v>
       </c>
       <c r="C26" t="s">
-        <v>128</v>
+        <v>325</v>
       </c>
       <c r="D26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E26" t="s">
+        <v>127</v>
+      </c>
+      <c r="F26" t="s">
         <v>246</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -2486,19 +2604,22 @@
         <v>153</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>326</v>
       </c>
       <c r="D27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E27" t="s">
+        <v>127</v>
+      </c>
+      <c r="F27" t="s">
         <v>247</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -2506,19 +2627,22 @@
         <v>154</v>
       </c>
       <c r="C28" t="s">
-        <v>128</v>
+        <v>327</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E28" t="s">
+        <v>127</v>
+      </c>
+      <c r="F28" t="s">
         <v>248</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -2526,19 +2650,22 @@
         <v>155</v>
       </c>
       <c r="C29" t="s">
-        <v>128</v>
+        <v>328</v>
       </c>
       <c r="D29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E29" t="s">
+        <v>127</v>
+      </c>
+      <c r="F29" t="s">
         <v>249</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>41</v>
       </c>
@@ -2546,19 +2673,22 @@
         <v>156</v>
       </c>
       <c r="C30" t="s">
-        <v>128</v>
+        <v>329</v>
       </c>
       <c r="D30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E30" t="s">
+        <v>127</v>
+      </c>
+      <c r="F30" t="s">
         <v>250</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -2566,19 +2696,22 @@
         <v>157</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>330</v>
       </c>
       <c r="D31" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E31" t="s">
+        <v>127</v>
+      </c>
+      <c r="F31" t="s">
         <v>251</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>43</v>
       </c>
@@ -2586,19 +2719,22 @@
         <v>158</v>
       </c>
       <c r="C32" t="s">
-        <v>128</v>
+        <v>331</v>
       </c>
       <c r="D32" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E32" t="s">
+        <v>127</v>
+      </c>
+      <c r="F32" t="s">
         <v>252</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>44</v>
       </c>
@@ -2606,19 +2742,22 @@
         <v>159</v>
       </c>
       <c r="C33" t="s">
-        <v>128</v>
+        <v>322</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E33" t="s">
+        <v>127</v>
+      </c>
+      <c r="F33" t="s">
         <v>253</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>45</v>
       </c>
@@ -2626,19 +2765,22 @@
         <v>160</v>
       </c>
       <c r="C34" t="s">
-        <v>128</v>
+        <v>323</v>
       </c>
       <c r="D34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E34" t="s">
+        <v>127</v>
+      </c>
+      <c r="F34" t="s">
         <v>254</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>46</v>
       </c>
@@ -2646,19 +2788,22 @@
         <v>161</v>
       </c>
       <c r="C35" t="s">
-        <v>128</v>
+        <v>324</v>
       </c>
       <c r="D35" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E35" t="s">
+        <v>127</v>
+      </c>
+      <c r="F35" t="s">
         <v>255</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>47</v>
       </c>
@@ -2666,19 +2811,22 @@
         <v>162</v>
       </c>
       <c r="C36" t="s">
-        <v>128</v>
+        <v>325</v>
       </c>
       <c r="D36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E36" t="s">
+        <v>127</v>
+      </c>
+      <c r="F36" t="s">
         <v>256</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>48</v>
       </c>
@@ -2686,19 +2834,22 @@
         <v>163</v>
       </c>
       <c r="C37" t="s">
-        <v>128</v>
+        <v>326</v>
       </c>
       <c r="D37" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E37" t="s">
+        <v>127</v>
+      </c>
+      <c r="F37" t="s">
         <v>257</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>49</v>
       </c>
@@ -2706,19 +2857,22 @@
         <v>164</v>
       </c>
       <c r="C38" t="s">
-        <v>128</v>
+        <v>327</v>
       </c>
       <c r="D38" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E38" t="s">
+        <v>127</v>
+      </c>
+      <c r="F38" t="s">
         <v>258</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>50</v>
       </c>
@@ -2726,19 +2880,22 @@
         <v>165</v>
       </c>
       <c r="C39" t="s">
-        <v>128</v>
+        <v>328</v>
       </c>
       <c r="D39" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E39" t="s">
+        <v>127</v>
+      </c>
+      <c r="F39" t="s">
         <v>259</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>51</v>
       </c>
@@ -2746,19 +2903,22 @@
         <v>166</v>
       </c>
       <c r="C40" t="s">
-        <v>128</v>
+        <v>329</v>
       </c>
       <c r="D40" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E40" t="s">
+        <v>127</v>
+      </c>
+      <c r="F40" t="s">
         <v>260</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>52</v>
       </c>
@@ -2766,19 +2926,22 @@
         <v>167</v>
       </c>
       <c r="C41" t="s">
-        <v>128</v>
+        <v>330</v>
       </c>
       <c r="D41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E41" t="s">
+        <v>127</v>
+      </c>
+      <c r="F41" t="s">
         <v>261</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>53</v>
       </c>
@@ -2786,19 +2949,22 @@
         <v>168</v>
       </c>
       <c r="C42" t="s">
-        <v>128</v>
+        <v>331</v>
       </c>
       <c r="D42" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E42" t="s">
+        <v>127</v>
+      </c>
+      <c r="F42" t="s">
         <v>262</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>54</v>
       </c>
@@ -2806,19 +2972,22 @@
         <v>169</v>
       </c>
       <c r="C43" t="s">
-        <v>128</v>
+        <v>322</v>
       </c>
       <c r="D43" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E43" t="s">
+        <v>127</v>
+      </c>
+      <c r="F43" t="s">
         <v>263</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>55</v>
       </c>
@@ -2826,19 +2995,22 @@
         <v>170</v>
       </c>
       <c r="C44" t="s">
-        <v>128</v>
+        <v>323</v>
       </c>
       <c r="D44" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E44" t="s">
+        <v>127</v>
+      </c>
+      <c r="F44" t="s">
         <v>264</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>56</v>
       </c>
@@ -2846,19 +3018,22 @@
         <v>171</v>
       </c>
       <c r="C45" t="s">
-        <v>128</v>
+        <v>324</v>
       </c>
       <c r="D45" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E45" t="s">
+        <v>127</v>
+      </c>
+      <c r="F45" t="s">
         <v>265</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>57</v>
       </c>
@@ -2866,19 +3041,22 @@
         <v>172</v>
       </c>
       <c r="C46" t="s">
-        <v>128</v>
+        <v>325</v>
       </c>
       <c r="D46" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E46" t="s">
+        <v>127</v>
+      </c>
+      <c r="F46" t="s">
         <v>266</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>58</v>
       </c>
@@ -2886,19 +3064,22 @@
         <v>173</v>
       </c>
       <c r="C47" t="s">
-        <v>128</v>
+        <v>326</v>
       </c>
       <c r="D47" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E47" t="s">
+        <v>127</v>
+      </c>
+      <c r="F47" t="s">
         <v>267</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>59</v>
       </c>
@@ -2906,19 +3087,22 @@
         <v>174</v>
       </c>
       <c r="C48" t="s">
-        <v>128</v>
+        <v>327</v>
       </c>
       <c r="D48" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E48" t="s">
+        <v>127</v>
+      </c>
+      <c r="F48" t="s">
         <v>268</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>60</v>
       </c>
@@ -2926,19 +3110,22 @@
         <v>175</v>
       </c>
       <c r="C49" t="s">
-        <v>128</v>
+        <v>328</v>
       </c>
       <c r="D49" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E49" t="s">
+        <v>127</v>
+      </c>
+      <c r="F49" t="s">
         <v>122</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>61</v>
       </c>
@@ -2946,19 +3133,22 @@
         <v>176</v>
       </c>
       <c r="C50" t="s">
-        <v>128</v>
+        <v>329</v>
       </c>
       <c r="D50" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E50" t="s">
+        <v>127</v>
+      </c>
+      <c r="F50" t="s">
         <v>269</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>62</v>
       </c>
@@ -2966,19 +3156,22 @@
         <v>177</v>
       </c>
       <c r="C51" t="s">
-        <v>128</v>
+        <v>330</v>
       </c>
       <c r="D51" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E51" t="s">
+        <v>127</v>
+      </c>
+      <c r="F51" t="s">
         <v>270</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -2986,19 +3179,22 @@
         <v>178</v>
       </c>
       <c r="C52" t="s">
-        <v>128</v>
+        <v>331</v>
       </c>
       <c r="D52" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E52" t="s">
+        <v>127</v>
+      </c>
+      <c r="F52" t="s">
         <v>271</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>64</v>
       </c>
@@ -3006,19 +3202,22 @@
         <v>179</v>
       </c>
       <c r="C53" t="s">
-        <v>128</v>
+        <v>322</v>
       </c>
       <c r="D53" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E53" t="s">
+        <v>127</v>
+      </c>
+      <c r="F53" t="s">
         <v>272</v>
       </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>66</v>
       </c>
@@ -3026,19 +3225,22 @@
         <v>180</v>
       </c>
       <c r="C54" t="s">
-        <v>128</v>
+        <v>323</v>
       </c>
       <c r="D54" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E54" t="s">
+        <v>127</v>
+      </c>
+      <c r="F54" t="s">
         <v>273</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>67</v>
       </c>
@@ -3046,19 +3248,22 @@
         <v>181</v>
       </c>
       <c r="C55" t="s">
-        <v>128</v>
+        <v>324</v>
       </c>
       <c r="D55" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E55" t="s">
+        <v>127</v>
+      </c>
+      <c r="F55" t="s">
         <v>274</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>68</v>
       </c>
@@ -3066,19 +3271,22 @@
         <v>182</v>
       </c>
       <c r="C56" t="s">
-        <v>128</v>
+        <v>325</v>
       </c>
       <c r="D56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E56" t="s">
+        <v>127</v>
+      </c>
+      <c r="F56" t="s">
         <v>275</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>69</v>
       </c>
@@ -3086,19 +3294,22 @@
         <v>183</v>
       </c>
       <c r="C57" t="s">
-        <v>128</v>
+        <v>326</v>
       </c>
       <c r="D57" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E57" t="s">
+        <v>127</v>
+      </c>
+      <c r="F57" t="s">
         <v>276</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>70</v>
       </c>
@@ -3106,19 +3317,22 @@
         <v>184</v>
       </c>
       <c r="C58" t="s">
-        <v>128</v>
+        <v>327</v>
       </c>
       <c r="D58" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E58" t="s">
+        <v>127</v>
+      </c>
+      <c r="F58" t="s">
         <v>277</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>71</v>
       </c>
@@ -3126,19 +3340,22 @@
         <v>185</v>
       </c>
       <c r="C59" t="s">
-        <v>128</v>
+        <v>328</v>
       </c>
       <c r="D59" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E59" t="s">
+        <v>127</v>
+      </c>
+      <c r="F59" t="s">
         <v>278</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>72</v>
       </c>
@@ -3146,19 +3363,22 @@
         <v>186</v>
       </c>
       <c r="C60" t="s">
-        <v>128</v>
+        <v>329</v>
       </c>
       <c r="D60" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E60" t="s">
+        <v>127</v>
+      </c>
+      <c r="F60" t="s">
         <v>279</v>
       </c>
-      <c r="F60" t="s">
+      <c r="G60" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>73</v>
       </c>
@@ -3166,19 +3386,22 @@
         <v>187</v>
       </c>
       <c r="C61" t="s">
-        <v>128</v>
+        <v>330</v>
       </c>
       <c r="D61" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E61" t="s">
+        <v>127</v>
+      </c>
+      <c r="F61" t="s">
         <v>280</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>74</v>
       </c>
@@ -3186,19 +3409,22 @@
         <v>188</v>
       </c>
       <c r="C62" t="s">
-        <v>128</v>
+        <v>331</v>
       </c>
       <c r="D62" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E62" t="s">
+        <v>127</v>
+      </c>
+      <c r="F62" t="s">
         <v>123</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>75</v>
       </c>
@@ -3206,19 +3432,22 @@
         <v>189</v>
       </c>
       <c r="C63" t="s">
-        <v>128</v>
+        <v>322</v>
       </c>
       <c r="D63" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E63" t="s">
+        <v>127</v>
+      </c>
+      <c r="F63" t="s">
         <v>281</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>76</v>
       </c>
@@ -3226,19 +3455,22 @@
         <v>190</v>
       </c>
       <c r="C64" t="s">
-        <v>128</v>
+        <v>323</v>
       </c>
       <c r="D64" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E64" t="s">
+        <v>127</v>
+      </c>
+      <c r="F64" t="s">
         <v>282</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>77</v>
       </c>
@@ -3246,19 +3478,22 @@
         <v>191</v>
       </c>
       <c r="C65" t="s">
-        <v>128</v>
+        <v>324</v>
       </c>
       <c r="D65" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E65" t="s">
+        <v>127</v>
+      </c>
+      <c r="F65" t="s">
         <v>283</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>78</v>
       </c>
@@ -3266,19 +3501,22 @@
         <v>192</v>
       </c>
       <c r="C66" t="s">
-        <v>128</v>
+        <v>325</v>
       </c>
       <c r="D66" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E66" t="s">
+        <v>127</v>
+      </c>
+      <c r="F66" t="s">
         <v>284</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>79</v>
       </c>
@@ -3286,19 +3524,22 @@
         <v>193</v>
       </c>
       <c r="C67" t="s">
-        <v>128</v>
+        <v>326</v>
       </c>
       <c r="D67" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E67" t="s">
+        <v>127</v>
+      </c>
+      <c r="F67" t="s">
         <v>285</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>80</v>
       </c>
@@ -3306,19 +3547,22 @@
         <v>194</v>
       </c>
       <c r="C68" t="s">
-        <v>128</v>
+        <v>327</v>
       </c>
       <c r="D68" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E68" t="s">
+        <v>127</v>
+      </c>
+      <c r="F68" t="s">
         <v>286</v>
       </c>
-      <c r="F68" t="s">
+      <c r="G68" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>81</v>
       </c>
@@ -3326,19 +3570,22 @@
         <v>195</v>
       </c>
       <c r="C69" t="s">
-        <v>128</v>
+        <v>328</v>
       </c>
       <c r="D69" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E69" t="s">
+        <v>127</v>
+      </c>
+      <c r="F69" t="s">
         <v>287</v>
       </c>
-      <c r="F69" t="s">
+      <c r="G69" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>82</v>
       </c>
@@ -3346,19 +3593,22 @@
         <v>196</v>
       </c>
       <c r="C70" t="s">
-        <v>128</v>
+        <v>329</v>
       </c>
       <c r="D70" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E70" t="s">
+        <v>127</v>
+      </c>
+      <c r="F70" t="s">
         <v>288</v>
       </c>
-      <c r="F70" t="s">
+      <c r="G70" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>83</v>
       </c>
@@ -3366,19 +3616,22 @@
         <v>197</v>
       </c>
       <c r="C71" t="s">
-        <v>128</v>
+        <v>330</v>
       </c>
       <c r="D71" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E71" t="s">
+        <v>127</v>
+      </c>
+      <c r="F71" t="s">
         <v>289</v>
       </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>84</v>
       </c>
@@ -3386,19 +3639,22 @@
         <v>198</v>
       </c>
       <c r="C72" t="s">
-        <v>128</v>
+        <v>331</v>
       </c>
       <c r="D72" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E72" t="s">
+        <v>127</v>
+      </c>
+      <c r="F72" t="s">
         <v>290</v>
       </c>
-      <c r="F72" t="s">
+      <c r="G72" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>85</v>
       </c>
@@ -3406,19 +3662,22 @@
         <v>199</v>
       </c>
       <c r="C73" t="s">
-        <v>128</v>
+        <v>322</v>
       </c>
       <c r="D73" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E73" t="s">
+        <v>127</v>
+      </c>
+      <c r="F73" t="s">
         <v>291</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>86</v>
       </c>
@@ -3426,19 +3685,22 @@
         <v>200</v>
       </c>
       <c r="C74" t="s">
-        <v>128</v>
+        <v>323</v>
       </c>
       <c r="D74" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E74" t="s">
+        <v>127</v>
+      </c>
+      <c r="F74" t="s">
         <v>292</v>
       </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>87</v>
       </c>
@@ -3446,19 +3708,22 @@
         <v>201</v>
       </c>
       <c r="C75" t="s">
-        <v>128</v>
+        <v>324</v>
       </c>
       <c r="D75" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E75" t="s">
+        <v>127</v>
+      </c>
+      <c r="F75" t="s">
         <v>293</v>
       </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>88</v>
       </c>
@@ -3466,19 +3731,22 @@
         <v>202</v>
       </c>
       <c r="C76" t="s">
-        <v>128</v>
+        <v>325</v>
       </c>
       <c r="D76" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E76" t="s">
+        <v>127</v>
+      </c>
+      <c r="F76" t="s">
         <v>294</v>
       </c>
-      <c r="F76" t="s">
+      <c r="G76" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>89</v>
       </c>
@@ -3486,19 +3754,22 @@
         <v>203</v>
       </c>
       <c r="C77" t="s">
-        <v>128</v>
+        <v>326</v>
       </c>
       <c r="D77" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E77" t="s">
+        <v>127</v>
+      </c>
+      <c r="F77" t="s">
         <v>124</v>
       </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>90</v>
       </c>
@@ -3506,19 +3777,22 @@
         <v>204</v>
       </c>
       <c r="C78" t="s">
-        <v>128</v>
+        <v>327</v>
       </c>
       <c r="D78" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E78" t="s">
+        <v>127</v>
+      </c>
+      <c r="F78" t="s">
         <v>295</v>
       </c>
-      <c r="F78" t="s">
+      <c r="G78" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>91</v>
       </c>
@@ -3526,19 +3800,22 @@
         <v>205</v>
       </c>
       <c r="C79" t="s">
-        <v>128</v>
+        <v>328</v>
       </c>
       <c r="D79" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E79" t="s">
+        <v>127</v>
+      </c>
+      <c r="F79" t="s">
         <v>296</v>
       </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>92</v>
       </c>
@@ -3546,19 +3823,22 @@
         <v>206</v>
       </c>
       <c r="C80" t="s">
-        <v>128</v>
+        <v>329</v>
       </c>
       <c r="D80" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E80" t="s">
+        <v>127</v>
+      </c>
+      <c r="F80" t="s">
         <v>297</v>
       </c>
-      <c r="F80" t="s">
+      <c r="G80" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>93</v>
       </c>
@@ -3566,19 +3846,22 @@
         <v>207</v>
       </c>
       <c r="C81" t="s">
-        <v>128</v>
+        <v>330</v>
       </c>
       <c r="D81" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E81" t="s">
+        <v>127</v>
+      </c>
+      <c r="F81" t="s">
         <v>298</v>
       </c>
-      <c r="F81" t="s">
+      <c r="G81" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>94</v>
       </c>
@@ -3586,19 +3869,22 @@
         <v>208</v>
       </c>
       <c r="C82" t="s">
-        <v>128</v>
+        <v>331</v>
       </c>
       <c r="D82" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E82" t="s">
+        <v>127</v>
+      </c>
+      <c r="F82" t="s">
         <v>299</v>
       </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>95</v>
       </c>
@@ -3606,19 +3892,22 @@
         <v>209</v>
       </c>
       <c r="C83" t="s">
-        <v>128</v>
+        <v>322</v>
       </c>
       <c r="D83" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E83" t="s">
+        <v>127</v>
+      </c>
+      <c r="F83" t="s">
         <v>300</v>
       </c>
-      <c r="F83" t="s">
+      <c r="G83" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>97</v>
       </c>
@@ -3626,19 +3915,22 @@
         <v>210</v>
       </c>
       <c r="C84" t="s">
-        <v>128</v>
+        <v>323</v>
       </c>
       <c r="D84" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E84" t="s">
+        <v>127</v>
+      </c>
+      <c r="F84" t="s">
         <v>301</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>98</v>
       </c>
@@ -3646,19 +3938,22 @@
         <v>211</v>
       </c>
       <c r="C85" t="s">
-        <v>128</v>
+        <v>324</v>
       </c>
       <c r="D85" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E85" t="s">
+        <v>127</v>
+      </c>
+      <c r="F85" t="s">
         <v>302</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>99</v>
       </c>
@@ -3666,19 +3961,22 @@
         <v>212</v>
       </c>
       <c r="C86" t="s">
-        <v>128</v>
+        <v>325</v>
       </c>
       <c r="D86" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E86" t="s">
+        <v>127</v>
+      </c>
+      <c r="F86" t="s">
         <v>303</v>
       </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>100</v>
       </c>
@@ -3686,19 +3984,22 @@
         <v>213</v>
       </c>
       <c r="C87" t="s">
-        <v>128</v>
+        <v>326</v>
       </c>
       <c r="D87" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E87" t="s">
+        <v>127</v>
+      </c>
+      <c r="F87" t="s">
         <v>304</v>
       </c>
-      <c r="F87" t="s">
+      <c r="G87" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>101</v>
       </c>
@@ -3706,19 +4007,22 @@
         <v>214</v>
       </c>
       <c r="C88" t="s">
-        <v>128</v>
+        <v>327</v>
       </c>
       <c r="D88" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E88" t="s">
+        <v>127</v>
+      </c>
+      <c r="F88" t="s">
         <v>305</v>
       </c>
-      <c r="F88" t="s">
+      <c r="G88" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>102</v>
       </c>
@@ -3726,19 +4030,22 @@
         <v>215</v>
       </c>
       <c r="C89" t="s">
-        <v>128</v>
+        <v>328</v>
       </c>
       <c r="D89" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E89" t="s">
+        <v>127</v>
+      </c>
+      <c r="F89" t="s">
         <v>306</v>
       </c>
-      <c r="F89" t="s">
+      <c r="G89" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>103</v>
       </c>
@@ -3746,19 +4053,22 @@
         <v>216</v>
       </c>
       <c r="C90" t="s">
-        <v>128</v>
+        <v>329</v>
       </c>
       <c r="D90" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E90" t="s">
+        <v>127</v>
+      </c>
+      <c r="F90" t="s">
         <v>307</v>
       </c>
-      <c r="F90" t="s">
+      <c r="G90" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>104</v>
       </c>
@@ -3766,19 +4076,22 @@
         <v>217</v>
       </c>
       <c r="C91" t="s">
-        <v>128</v>
+        <v>330</v>
       </c>
       <c r="D91" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E91" t="s">
+        <v>127</v>
+      </c>
+      <c r="F91" t="s">
         <v>308</v>
       </c>
-      <c r="F91" t="s">
+      <c r="G91" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>105</v>
       </c>
@@ -3786,19 +4099,22 @@
         <v>218</v>
       </c>
       <c r="C92" t="s">
-        <v>128</v>
+        <v>331</v>
       </c>
       <c r="D92" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E92" t="s">
+        <v>127</v>
+      </c>
+      <c r="F92" t="s">
         <v>309</v>
       </c>
-      <c r="F92" t="s">
+      <c r="G92" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>106</v>
       </c>
@@ -3806,19 +4122,22 @@
         <v>219</v>
       </c>
       <c r="C93" t="s">
-        <v>128</v>
+        <v>322</v>
       </c>
       <c r="D93" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E93" t="s">
+        <v>127</v>
+      </c>
+      <c r="F93" t="s">
         <v>310</v>
       </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>107</v>
       </c>
@@ -3826,19 +4145,22 @@
         <v>220</v>
       </c>
       <c r="C94" t="s">
-        <v>128</v>
+        <v>323</v>
       </c>
       <c r="D94" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E94" t="s">
+        <v>127</v>
+      </c>
+      <c r="F94" t="s">
         <v>311</v>
       </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>108</v>
       </c>
@@ -3846,19 +4168,22 @@
         <v>221</v>
       </c>
       <c r="C95" t="s">
-        <v>128</v>
+        <v>324</v>
       </c>
       <c r="D95" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E95" t="s">
+        <v>127</v>
+      </c>
+      <c r="F95" t="s">
         <v>312</v>
       </c>
-      <c r="F95" t="s">
+      <c r="G95" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>109</v>
       </c>
@@ -3866,19 +4191,22 @@
         <v>222</v>
       </c>
       <c r="C96" t="s">
-        <v>128</v>
+        <v>325</v>
       </c>
       <c r="D96" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E96" t="s">
+        <v>127</v>
+      </c>
+      <c r="F96" t="s">
         <v>313</v>
       </c>
-      <c r="F96" t="s">
+      <c r="G96" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>110</v>
       </c>
@@ -3886,19 +4214,22 @@
         <v>223</v>
       </c>
       <c r="C97" t="s">
-        <v>128</v>
+        <v>326</v>
       </c>
       <c r="D97" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E97" t="s">
+        <v>127</v>
+      </c>
+      <c r="F97" t="s">
         <v>314</v>
       </c>
-      <c r="F97" t="s">
+      <c r="G97" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>111</v>
       </c>
@@ -3906,19 +4237,22 @@
         <v>224</v>
       </c>
       <c r="C98" t="s">
-        <v>128</v>
+        <v>327</v>
       </c>
       <c r="D98" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E98" t="s">
+        <v>127</v>
+      </c>
+      <c r="F98" t="s">
         <v>315</v>
       </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>112</v>
       </c>
@@ -3926,19 +4260,22 @@
         <v>225</v>
       </c>
       <c r="C99" t="s">
-        <v>128</v>
+        <v>328</v>
       </c>
       <c r="D99" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E99" t="s">
+        <v>127</v>
+      </c>
+      <c r="F99" t="s">
         <v>316</v>
       </c>
-      <c r="F99" t="s">
+      <c r="G99" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>113</v>
       </c>
@@ -3946,19 +4283,22 @@
         <v>226</v>
       </c>
       <c r="C100" t="s">
-        <v>128</v>
+        <v>329</v>
       </c>
       <c r="D100" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E100" t="s">
+        <v>127</v>
+      </c>
+      <c r="F100" t="s">
         <v>317</v>
       </c>
-      <c r="F100" t="s">
+      <c r="G100" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>114</v>
       </c>
@@ -3966,19 +4306,22 @@
         <v>227</v>
       </c>
       <c r="C101" t="s">
-        <v>128</v>
+        <v>330</v>
       </c>
       <c r="D101" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E101" t="s">
+        <v>127</v>
+      </c>
+      <c r="F101" t="s">
         <v>318</v>
       </c>
-      <c r="F101" t="s">
+      <c r="G101" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>115</v>
       </c>
@@ -3986,15 +4329,18 @@
         <v>228</v>
       </c>
       <c r="C102" t="s">
-        <v>128</v>
+        <v>331</v>
       </c>
       <c r="D102" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E102" t="s">
+        <v>127</v>
+      </c>
+      <c r="F102" t="s">
         <v>319</v>
       </c>
-      <c r="F102" t="s">
+      <c r="G102" t="s">
         <v>96</v>
       </c>
     </row>

--- a/Assets/Config/Holmas_AgencyBuildingTable.xlsx
+++ b/Assets/Config/Holmas_AgencyBuildingTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Holmas\Assets\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D15D30-FF41-4871-BFEF-278F578CF36D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA46918-7FAF-4240-8818-3361962556C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,12 +36,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="332">
   <si>
-    <t>城市阶段id</t>
-  </si>
-  <si>
-    <t>城市名</t>
-  </si>
-  <si>
     <t>宣传功能id数组</t>
   </si>
   <si>
@@ -1037,6 +1031,14 @@
   </si>
   <si>
     <t>Textures/buildings/building10.png</t>
+  </si>
+  <si>
+    <t>城市名</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>城市阶段id</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1991,6 +1993,7 @@
   <dimension ref="A1:G102"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="16.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
@@ -2000,2352 +2003,2353 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>320</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C7" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C8" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F8" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C9" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F9" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C10" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C13" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D13" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E13" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F13" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C14" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D14" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E14" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C15" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D15" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F15" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C16" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E16" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F16" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E17" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F17" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C18" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D18" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E18" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F18" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G18" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C19" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F19" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C20" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F20" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G20" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C21" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D21" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E21" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F21" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G21" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C22" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D22" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F22" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C23" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D23" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C24" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E24" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F24" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C25" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D25" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E25" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F25" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C26" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D26" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E26" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F26" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C27" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D27" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E27" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C28" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E28" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F28" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G28" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C29" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D29" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E29" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F29" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G29" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C30" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D30" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E30" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F30" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G30" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C31" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D31" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E31" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F31" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G31" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C32" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D32" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E32" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F32" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G32" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C33" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D33" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E33" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F33" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G33" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C34" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E34" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F34" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G34" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C35" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D35" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F35" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G35" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C36" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D36" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E36" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F36" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G36" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C37" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D37" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E37" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F37" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G37" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C38" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D38" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E38" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F38" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C39" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D39" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E39" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F39" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G39" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C40" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D40" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E40" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F40" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G40" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C41" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D41" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E41" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F41" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G41" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C42" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D42" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E42" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F42" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G42" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C43" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D43" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E43" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G43" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C44" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D44" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E44" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F44" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G44" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B45" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C45" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D45" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E45" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F45" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G45" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C46" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D46" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F46" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G46" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B47" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C47" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D47" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E47" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F47" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G47" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B48" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C48" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D48" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E48" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F48" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G48" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B49" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C49" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D49" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E49" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F49" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G49" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B50" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C50" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D50" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E50" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F50" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G50" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B51" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C51" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D51" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E51" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F51" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G51" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B52" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C52" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D52" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E52" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F52" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G52" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B53" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C53" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D53" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E53" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F53" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G53" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B54" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C54" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D54" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E54" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F54" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G54" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B55" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C55" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D55" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E55" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F55" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G55" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B56" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C56" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D56" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E56" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F56" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G56" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B57" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C57" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D57" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E57" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F57" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G57" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B58" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C58" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D58" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E58" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F58" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G58" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B59" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C59" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D59" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E59" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F59" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G59" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B60" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C60" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D60" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E60" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F60" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G60" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B61" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C61" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D61" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E61" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F61" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G61" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B62" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C62" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D62" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E62" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F62" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G62" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B63" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C63" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D63" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E63" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F63" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G63" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B64" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C64" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E64" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F64" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G64" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B65" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C65" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D65" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E65" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F65" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G65" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B66" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C66" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D66" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E66" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F66" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G66" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B67" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C67" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D67" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E67" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F67" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G67" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B68" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C68" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D68" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E68" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F68" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G68" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B69" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C69" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D69" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E69" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F69" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G69" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B70" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C70" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D70" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E70" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F70" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G70" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B71" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C71" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D71" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E71" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F71" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G71" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B72" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C72" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D72" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E72" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F72" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G72" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B73" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C73" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D73" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E73" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F73" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G73" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B74" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C74" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D74" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E74" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F74" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G74" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B75" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C75" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D75" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E75" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F75" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G75" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B76" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C76" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D76" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E76" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F76" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G76" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B77" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C77" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D77" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E77" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F77" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G77" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B78" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C78" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D78" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E78" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F78" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G78" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B79" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C79" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D79" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E79" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F79" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G79" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B80" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C80" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D80" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E80" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F80" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G80" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B81" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C81" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D81" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E81" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F81" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G81" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B82" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C82" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D82" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E82" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F82" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G82" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B83" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C83" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D83" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E83" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F83" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G83" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B84" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C84" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D84" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E84" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F84" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B85" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C85" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D85" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E85" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F85" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G85" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B86" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C86" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D86" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E86" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F86" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G86" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B87" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C87" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D87" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E87" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F87" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G87" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B88" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C88" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D88" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E88" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F88" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G88" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B89" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C89" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D89" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E89" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F89" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G89" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B90" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C90" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D90" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E90" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F90" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G90" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B91" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C91" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D91" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E91" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F91" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G91" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B92" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C92" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D92" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E92" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F92" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G92" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B93" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C93" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D93" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E93" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F93" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G93" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B94" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C94" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D94" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E94" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F94" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G94" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B95" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C95" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D95" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E95" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F95" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G95" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B96" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C96" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D96" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E96" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F96" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G96" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B97" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C97" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D97" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E97" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F97" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G97" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B98" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C98" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D98" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E98" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F98" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G98" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B99" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C99" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D99" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E99" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F99" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G99" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B100" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C100" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D100" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E100" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F100" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G100" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B101" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C101" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D101" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E101" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F101" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G101" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B102" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C102" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D102" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E102" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F102" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G102" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Config/Holmas_AgencyBuildingTable.xlsx
+++ b/Assets/Config/Holmas_AgencyBuildingTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Holmas\Assets\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA46918-7FAF-4240-8818-3361962556C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BD2BCF-2B03-4967-8C61-005437787317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,9 +51,6 @@
     <t>agencyStageId</t>
   </si>
   <si>
-    <t>stageName</t>
-  </si>
-  <si>
     <t>promotionIds</t>
   </si>
   <si>
@@ -417,10 +414,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>leaflet;radio;tv</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>柳溪村</t>
   </si>
   <si>
@@ -1038,6 +1031,14 @@
   </si>
   <si>
     <t>城市阶段id</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>leaflet;radio;net</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>stageName</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2003,13 +2004,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
@@ -2029,2322 +2030,2322 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D3" t="s">
+        <v>330</v>
+      </c>
+      <c r="E3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G3" t="s">
         <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C3" t="s">
-        <v>320</v>
-      </c>
-      <c r="D3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C7" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C9" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D9" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F9" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C10" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C11" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C13" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F13" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C14" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D14" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C15" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D15" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F15" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C16" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D16" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F16" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C17" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F17" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C18" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F18" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C19" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F19" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C20" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F20" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C21" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D21" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F21" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C22" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D22" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F22" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" t="s">
+        <v>145</v>
+      </c>
+      <c r="C23" t="s">
+        <v>318</v>
+      </c>
+      <c r="D23" t="s">
+        <v>330</v>
+      </c>
+      <c r="E23" t="s">
+        <v>124</v>
+      </c>
+      <c r="F23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G23" t="s">
         <v>31</v>
-      </c>
-      <c r="B23" t="s">
-        <v>147</v>
-      </c>
-      <c r="C23" t="s">
-        <v>320</v>
-      </c>
-      <c r="D23" t="s">
-        <v>126</v>
-      </c>
-      <c r="E23" t="s">
-        <v>125</v>
-      </c>
-      <c r="F23" t="s">
-        <v>119</v>
-      </c>
-      <c r="G23" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C24" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D24" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F24" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C25" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D25" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F25" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C26" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D26" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F26" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C27" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D27" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F27" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C28" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D28" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F28" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C29" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D29" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F29" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C30" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D30" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F30" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C31" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D31" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F31" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C32" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D32" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F32" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C33" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D33" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F33" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C34" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D34" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E34" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F34" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B35" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C35" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D35" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E35" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F35" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B36" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C36" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D36" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C37" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D37" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F37" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B38" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C38" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D38" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E38" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F38" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B39" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C39" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D39" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E39" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F39" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B40" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C40" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D40" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F40" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B41" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C41" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D41" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F41" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G41" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B42" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C42" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D42" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F42" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B43" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C43" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D43" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E43" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F43" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B44" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D44" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E44" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F44" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B45" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C45" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D45" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E45" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F45" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B46" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C46" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D46" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F46" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B47" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C47" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D47" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E47" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F47" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B48" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C48" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D48" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E48" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F48" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B49" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C49" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D49" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E49" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F49" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B50" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C50" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D50" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F50" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B51" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C51" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D51" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F51" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B52" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C52" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D52" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E52" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G52" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" t="s">
+        <v>175</v>
+      </c>
+      <c r="C53" t="s">
+        <v>318</v>
+      </c>
+      <c r="D53" t="s">
+        <v>330</v>
+      </c>
+      <c r="E53" t="s">
+        <v>124</v>
+      </c>
+      <c r="F53" t="s">
+        <v>268</v>
+      </c>
+      <c r="G53" t="s">
         <v>62</v>
-      </c>
-      <c r="B53" t="s">
-        <v>177</v>
-      </c>
-      <c r="C53" t="s">
-        <v>320</v>
-      </c>
-      <c r="D53" t="s">
-        <v>126</v>
-      </c>
-      <c r="E53" t="s">
-        <v>125</v>
-      </c>
-      <c r="F53" t="s">
-        <v>270</v>
-      </c>
-      <c r="G53" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B54" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C54" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D54" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E54" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F54" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G54" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B55" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C55" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D55" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E55" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F55" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B56" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C56" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D56" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E56" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F56" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G56" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B57" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C57" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D57" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F57" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G57" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B58" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C58" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D58" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E58" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F58" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G58" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B59" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C59" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D59" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E59" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F59" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B60" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C60" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D60" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E60" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F60" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G60" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B61" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C61" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D61" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E61" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F61" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G61" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B62" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C62" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D62" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E62" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F62" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G62" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B63" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C63" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D63" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E63" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F63" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G63" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B64" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C64" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D64" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F64" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G64" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B65" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C65" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D65" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E65" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F65" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G65" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B66" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C66" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D66" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E66" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F66" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G66" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B67" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C67" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D67" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E67" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F67" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B68" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C68" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D68" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E68" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F68" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G68" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B69" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C69" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D69" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E69" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F69" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G69" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B70" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C70" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D70" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E70" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F70" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G70" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B71" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C71" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D71" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E71" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F71" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G71" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B72" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C72" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D72" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E72" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F72" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G72" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B73" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C73" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D73" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E73" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F73" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G73" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B74" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C74" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D74" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E74" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F74" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G74" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B75" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C75" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D75" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E75" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F75" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G75" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B76" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C76" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D76" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E76" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F76" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G76" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B77" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C77" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D77" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E77" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F77" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G77" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B78" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C78" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D78" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E78" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F78" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G78" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B79" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C79" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D79" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E79" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F79" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G79" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B80" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C80" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D80" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E80" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F80" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G80" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B81" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C81" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D81" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E81" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F81" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G81" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B82" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C82" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D82" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E82" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F82" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G82" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
+        <v>92</v>
+      </c>
+      <c r="B83" t="s">
+        <v>205</v>
+      </c>
+      <c r="C83" t="s">
+        <v>318</v>
+      </c>
+      <c r="D83" t="s">
+        <v>330</v>
+      </c>
+      <c r="E83" t="s">
+        <v>124</v>
+      </c>
+      <c r="F83" t="s">
+        <v>296</v>
+      </c>
+      <c r="G83" t="s">
         <v>93</v>
-      </c>
-      <c r="B83" t="s">
-        <v>207</v>
-      </c>
-      <c r="C83" t="s">
-        <v>320</v>
-      </c>
-      <c r="D83" t="s">
-        <v>126</v>
-      </c>
-      <c r="E83" t="s">
-        <v>125</v>
-      </c>
-      <c r="F83" t="s">
-        <v>298</v>
-      </c>
-      <c r="G83" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B84" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C84" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D84" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E84" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F84" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B85" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C85" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D85" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E85" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F85" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G85" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B86" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C86" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D86" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E86" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F86" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G86" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B87" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C87" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D87" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E87" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F87" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G87" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B88" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C88" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D88" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E88" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F88" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G88" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B89" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C89" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D89" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E89" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F89" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G89" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B90" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C90" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D90" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E90" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F90" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G90" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B91" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C91" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D91" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E91" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F91" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G91" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B92" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C92" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D92" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E92" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F92" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G92" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B93" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C93" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D93" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E93" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F93" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G93" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B94" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C94" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D94" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E94" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F94" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G94" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B95" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C95" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D95" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E95" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F95" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G95" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B96" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C96" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D96" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E96" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F96" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G96" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B97" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C97" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D97" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E97" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F97" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G97" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B98" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C98" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D98" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E98" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F98" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G98" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B99" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C99" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D99" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E99" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F99" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G99" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B100" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C100" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D100" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E100" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F100" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G100" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B101" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C101" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D101" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E101" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F101" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G101" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B102" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C102" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D102" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="E102" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F102" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G102" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Config/Holmas_AgencyBuildingTable.xlsx
+++ b/Assets/Config/Holmas_AgencyBuildingTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Holmas\Assets\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BD2BCF-2B03-4967-8C61-005437787317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6120A236-FFDD-48DD-9E31-91502C2FA7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="335">
   <si>
     <t>宣传功能id数组</t>
   </si>
@@ -1039,6 +1039,18 @@
   </si>
   <si>
     <t>stageName</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>宣传按钮图片路劲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>buttonImage</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Textures/NewUIRes/leaflet.png;Textures/NewUIRes/radio.png;Textures/NewUIRes/net.png;</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1991,18 +2003,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="16.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="73.4140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.6640625" customWidth="1"/>
+    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="73.4140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>329</v>
       </c>
@@ -2013,19 +2026,22 @@
         <v>316</v>
       </c>
       <c r="D1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2036,19 +2052,22 @@
         <v>317</v>
       </c>
       <c r="D2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>7</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2059,19 +2078,22 @@
         <v>318</v>
       </c>
       <c r="D3" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E3" t="s">
+        <v>330</v>
+      </c>
+      <c r="F3" t="s">
         <v>122</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>113</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -2082,19 +2104,22 @@
         <v>319</v>
       </c>
       <c r="D4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E4" t="s">
+        <v>330</v>
+      </c>
+      <c r="F4" t="s">
         <v>123</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>114</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2105,19 +2130,22 @@
         <v>320</v>
       </c>
       <c r="D5" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E5" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G5" t="s">
         <v>115</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -2128,19 +2156,22 @@
         <v>321</v>
       </c>
       <c r="D6" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E6" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F6" t="s">
+        <v>124</v>
+      </c>
+      <c r="G6" t="s">
         <v>116</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -2151,19 +2182,22 @@
         <v>322</v>
       </c>
       <c r="D7" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E7" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G7" t="s">
         <v>117</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -2174,19 +2208,22 @@
         <v>323</v>
       </c>
       <c r="D8" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E8" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F8" t="s">
+        <v>124</v>
+      </c>
+      <c r="G8" t="s">
         <v>225</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -2197,19 +2234,22 @@
         <v>324</v>
       </c>
       <c r="D9" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E9" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F9" t="s">
+        <v>124</v>
+      </c>
+      <c r="G9" t="s">
         <v>226</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -2220,19 +2260,22 @@
         <v>325</v>
       </c>
       <c r="D10" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E10" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F10" t="s">
+        <v>124</v>
+      </c>
+      <c r="G10" t="s">
         <v>227</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -2243,19 +2286,22 @@
         <v>326</v>
       </c>
       <c r="D11" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E11" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G11" t="s">
         <v>228</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -2266,19 +2312,22 @@
         <v>327</v>
       </c>
       <c r="D12" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E12" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F12" t="s">
+        <v>124</v>
+      </c>
+      <c r="G12" t="s">
         <v>229</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -2289,19 +2338,22 @@
         <v>318</v>
       </c>
       <c r="D13" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E13" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F13" t="s">
+        <v>124</v>
+      </c>
+      <c r="G13" t="s">
         <v>230</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -2312,19 +2364,22 @@
         <v>319</v>
       </c>
       <c r="D14" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E14" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F14" t="s">
+        <v>124</v>
+      </c>
+      <c r="G14" t="s">
         <v>231</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -2335,19 +2390,22 @@
         <v>320</v>
       </c>
       <c r="D15" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E15" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F15" t="s">
+        <v>124</v>
+      </c>
+      <c r="G15" t="s">
         <v>232</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -2358,19 +2416,22 @@
         <v>321</v>
       </c>
       <c r="D16" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E16" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F16" t="s">
+        <v>124</v>
+      </c>
+      <c r="G16" t="s">
         <v>233</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -2381,19 +2442,22 @@
         <v>322</v>
       </c>
       <c r="D17" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E17" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F17" t="s">
+        <v>124</v>
+      </c>
+      <c r="G17" t="s">
         <v>234</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -2404,19 +2468,22 @@
         <v>323</v>
       </c>
       <c r="D18" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E18" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F18" t="s">
+        <v>124</v>
+      </c>
+      <c r="G18" t="s">
         <v>235</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -2427,19 +2494,22 @@
         <v>324</v>
       </c>
       <c r="D19" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E19" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F19" t="s">
+        <v>124</v>
+      </c>
+      <c r="G19" t="s">
         <v>236</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -2450,19 +2520,22 @@
         <v>325</v>
       </c>
       <c r="D20" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E20" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F20" t="s">
+        <v>124</v>
+      </c>
+      <c r="G20" t="s">
         <v>237</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -2473,19 +2546,22 @@
         <v>326</v>
       </c>
       <c r="D21" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E21" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G21" t="s">
         <v>238</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -2496,19 +2572,22 @@
         <v>327</v>
       </c>
       <c r="D22" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E22" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F22" t="s">
+        <v>124</v>
+      </c>
+      <c r="G22" t="s">
         <v>239</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -2519,19 +2598,22 @@
         <v>318</v>
       </c>
       <c r="D23" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E23" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F23" t="s">
+        <v>124</v>
+      </c>
+      <c r="G23" t="s">
         <v>118</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -2542,19 +2624,22 @@
         <v>319</v>
       </c>
       <c r="D24" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E24" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F24" t="s">
+        <v>124</v>
+      </c>
+      <c r="G24" t="s">
         <v>240</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -2565,19 +2650,22 @@
         <v>320</v>
       </c>
       <c r="D25" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E25" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F25" t="s">
+        <v>124</v>
+      </c>
+      <c r="G25" t="s">
         <v>241</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -2588,19 +2676,22 @@
         <v>321</v>
       </c>
       <c r="D26" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E26" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F26" t="s">
+        <v>124</v>
+      </c>
+      <c r="G26" t="s">
         <v>242</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -2611,19 +2702,22 @@
         <v>322</v>
       </c>
       <c r="D27" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E27" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F27" t="s">
+        <v>124</v>
+      </c>
+      <c r="G27" t="s">
         <v>243</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -2634,19 +2728,22 @@
         <v>323</v>
       </c>
       <c r="D28" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E28" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F28" t="s">
+        <v>124</v>
+      </c>
+      <c r="G28" t="s">
         <v>244</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -2657,19 +2754,22 @@
         <v>324</v>
       </c>
       <c r="D29" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E29" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F29" t="s">
+        <v>124</v>
+      </c>
+      <c r="G29" t="s">
         <v>245</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -2680,19 +2780,22 @@
         <v>325</v>
       </c>
       <c r="D30" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E30" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F30" t="s">
+        <v>124</v>
+      </c>
+      <c r="G30" t="s">
         <v>246</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -2703,19 +2806,22 @@
         <v>326</v>
       </c>
       <c r="D31" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E31" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F31" t="s">
+        <v>124</v>
+      </c>
+      <c r="G31" t="s">
         <v>247</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -2726,19 +2832,22 @@
         <v>327</v>
       </c>
       <c r="D32" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E32" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F32" t="s">
+        <v>124</v>
+      </c>
+      <c r="G32" t="s">
         <v>248</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -2749,19 +2858,22 @@
         <v>318</v>
       </c>
       <c r="D33" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E33" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F33" t="s">
+        <v>124</v>
+      </c>
+      <c r="G33" t="s">
         <v>249</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -2772,19 +2884,22 @@
         <v>319</v>
       </c>
       <c r="D34" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E34" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F34" t="s">
+        <v>124</v>
+      </c>
+      <c r="G34" t="s">
         <v>250</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -2795,19 +2910,22 @@
         <v>320</v>
       </c>
       <c r="D35" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E35" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F35" t="s">
+        <v>124</v>
+      </c>
+      <c r="G35" t="s">
         <v>251</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -2818,19 +2936,22 @@
         <v>321</v>
       </c>
       <c r="D36" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E36" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F36" t="s">
+        <v>124</v>
+      </c>
+      <c r="G36" t="s">
         <v>252</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -2841,19 +2962,22 @@
         <v>322</v>
       </c>
       <c r="D37" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E37" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F37" t="s">
+        <v>124</v>
+      </c>
+      <c r="G37" t="s">
         <v>253</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -2864,19 +2988,22 @@
         <v>323</v>
       </c>
       <c r="D38" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E38" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F38" t="s">
+        <v>124</v>
+      </c>
+      <c r="G38" t="s">
         <v>254</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -2887,19 +3014,22 @@
         <v>324</v>
       </c>
       <c r="D39" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E39" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F39" t="s">
+        <v>124</v>
+      </c>
+      <c r="G39" t="s">
         <v>255</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>48</v>
       </c>
@@ -2910,19 +3040,22 @@
         <v>325</v>
       </c>
       <c r="D40" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E40" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F40" t="s">
+        <v>124</v>
+      </c>
+      <c r="G40" t="s">
         <v>256</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>49</v>
       </c>
@@ -2933,19 +3066,22 @@
         <v>326</v>
       </c>
       <c r="D41" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E41" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F41" t="s">
+        <v>124</v>
+      </c>
+      <c r="G41" t="s">
         <v>257</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -2956,19 +3092,22 @@
         <v>327</v>
       </c>
       <c r="D42" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E42" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F42" t="s">
+        <v>124</v>
+      </c>
+      <c r="G42" t="s">
         <v>258</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -2979,19 +3118,22 @@
         <v>318</v>
       </c>
       <c r="D43" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E43" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F43" t="s">
+        <v>124</v>
+      </c>
+      <c r="G43" t="s">
         <v>259</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>52</v>
       </c>
@@ -3002,19 +3144,22 @@
         <v>319</v>
       </c>
       <c r="D44" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E44" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F44" t="s">
+        <v>124</v>
+      </c>
+      <c r="G44" t="s">
         <v>260</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -3025,19 +3170,22 @@
         <v>320</v>
       </c>
       <c r="D45" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E45" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F45" t="s">
+        <v>124</v>
+      </c>
+      <c r="G45" t="s">
         <v>261</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>54</v>
       </c>
@@ -3048,19 +3196,22 @@
         <v>321</v>
       </c>
       <c r="D46" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E46" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F46" t="s">
+        <v>124</v>
+      </c>
+      <c r="G46" t="s">
         <v>262</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -3071,19 +3222,22 @@
         <v>322</v>
       </c>
       <c r="D47" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E47" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F47" t="s">
+        <v>124</v>
+      </c>
+      <c r="G47" t="s">
         <v>263</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -3094,19 +3248,22 @@
         <v>323</v>
       </c>
       <c r="D48" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E48" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F48" t="s">
+        <v>124</v>
+      </c>
+      <c r="G48" t="s">
         <v>264</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>57</v>
       </c>
@@ -3117,19 +3274,22 @@
         <v>324</v>
       </c>
       <c r="D49" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E49" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F49" t="s">
+        <v>124</v>
+      </c>
+      <c r="G49" t="s">
         <v>119</v>
       </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -3140,19 +3300,22 @@
         <v>325</v>
       </c>
       <c r="D50" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E50" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F50" t="s">
+        <v>124</v>
+      </c>
+      <c r="G50" t="s">
         <v>265</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>59</v>
       </c>
@@ -3163,19 +3326,22 @@
         <v>326</v>
       </c>
       <c r="D51" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E51" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F51" t="s">
+        <v>124</v>
+      </c>
+      <c r="G51" t="s">
         <v>266</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>60</v>
       </c>
@@ -3186,19 +3352,22 @@
         <v>327</v>
       </c>
       <c r="D52" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E52" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F52" t="s">
+        <v>124</v>
+      </c>
+      <c r="G52" t="s">
         <v>267</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>61</v>
       </c>
@@ -3209,19 +3378,22 @@
         <v>318</v>
       </c>
       <c r="D53" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E53" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F53" t="s">
+        <v>124</v>
+      </c>
+      <c r="G53" t="s">
         <v>268</v>
       </c>
-      <c r="G53" t="s">
+      <c r="H53" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>63</v>
       </c>
@@ -3232,19 +3404,22 @@
         <v>319</v>
       </c>
       <c r="D54" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E54" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F54" t="s">
+        <v>124</v>
+      </c>
+      <c r="G54" t="s">
         <v>269</v>
       </c>
-      <c r="G54" t="s">
+      <c r="H54" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>64</v>
       </c>
@@ -3255,19 +3430,22 @@
         <v>320</v>
       </c>
       <c r="D55" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E55" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F55" t="s">
+        <v>124</v>
+      </c>
+      <c r="G55" t="s">
         <v>270</v>
       </c>
-      <c r="G55" t="s">
+      <c r="H55" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>65</v>
       </c>
@@ -3278,19 +3456,22 @@
         <v>321</v>
       </c>
       <c r="D56" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E56" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F56" t="s">
+        <v>124</v>
+      </c>
+      <c r="G56" t="s">
         <v>271</v>
       </c>
-      <c r="G56" t="s">
+      <c r="H56" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>66</v>
       </c>
@@ -3301,19 +3482,22 @@
         <v>322</v>
       </c>
       <c r="D57" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E57" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F57" t="s">
+        <v>124</v>
+      </c>
+      <c r="G57" t="s">
         <v>272</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>67</v>
       </c>
@@ -3324,19 +3508,22 @@
         <v>323</v>
       </c>
       <c r="D58" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E58" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F58" t="s">
+        <v>124</v>
+      </c>
+      <c r="G58" t="s">
         <v>273</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>68</v>
       </c>
@@ -3347,19 +3534,22 @@
         <v>324</v>
       </c>
       <c r="D59" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E59" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F59" t="s">
+        <v>124</v>
+      </c>
+      <c r="G59" t="s">
         <v>274</v>
       </c>
-      <c r="G59" t="s">
+      <c r="H59" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -3370,19 +3560,22 @@
         <v>325</v>
       </c>
       <c r="D60" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E60" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F60" t="s">
+        <v>124</v>
+      </c>
+      <c r="G60" t="s">
         <v>275</v>
       </c>
-      <c r="G60" t="s">
+      <c r="H60" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>70</v>
       </c>
@@ -3393,19 +3586,22 @@
         <v>326</v>
       </c>
       <c r="D61" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E61" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F61" t="s">
+        <v>124</v>
+      </c>
+      <c r="G61" t="s">
         <v>276</v>
       </c>
-      <c r="G61" t="s">
+      <c r="H61" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>71</v>
       </c>
@@ -3416,19 +3612,22 @@
         <v>327</v>
       </c>
       <c r="D62" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E62" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F62" t="s">
+        <v>124</v>
+      </c>
+      <c r="G62" t="s">
         <v>120</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>72</v>
       </c>
@@ -3439,19 +3638,22 @@
         <v>318</v>
       </c>
       <c r="D63" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E63" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F63" t="s">
+        <v>124</v>
+      </c>
+      <c r="G63" t="s">
         <v>277</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>73</v>
       </c>
@@ -3462,19 +3664,22 @@
         <v>319</v>
       </c>
       <c r="D64" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E64" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F64" t="s">
+        <v>124</v>
+      </c>
+      <c r="G64" t="s">
         <v>278</v>
       </c>
-      <c r="G64" t="s">
+      <c r="H64" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>74</v>
       </c>
@@ -3485,19 +3690,22 @@
         <v>320</v>
       </c>
       <c r="D65" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E65" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F65" t="s">
+        <v>124</v>
+      </c>
+      <c r="G65" t="s">
         <v>279</v>
       </c>
-      <c r="G65" t="s">
+      <c r="H65" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>75</v>
       </c>
@@ -3508,19 +3716,22 @@
         <v>321</v>
       </c>
       <c r="D66" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E66" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F66" t="s">
+        <v>124</v>
+      </c>
+      <c r="G66" t="s">
         <v>280</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>76</v>
       </c>
@@ -3531,19 +3742,22 @@
         <v>322</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E67" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F67" t="s">
+        <v>124</v>
+      </c>
+      <c r="G67" t="s">
         <v>281</v>
       </c>
-      <c r="G67" t="s">
+      <c r="H67" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -3554,19 +3768,22 @@
         <v>323</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E68" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F68" t="s">
+        <v>124</v>
+      </c>
+      <c r="G68" t="s">
         <v>282</v>
       </c>
-      <c r="G68" t="s">
+      <c r="H68" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -3577,19 +3794,22 @@
         <v>324</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E69" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F69" t="s">
+        <v>124</v>
+      </c>
+      <c r="G69" t="s">
         <v>283</v>
       </c>
-      <c r="G69" t="s">
+      <c r="H69" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -3600,19 +3820,22 @@
         <v>325</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E70" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F70" t="s">
+        <v>124</v>
+      </c>
+      <c r="G70" t="s">
         <v>284</v>
       </c>
-      <c r="G70" t="s">
+      <c r="H70" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>80</v>
       </c>
@@ -3623,19 +3846,22 @@
         <v>326</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E71" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F71" t="s">
+        <v>124</v>
+      </c>
+      <c r="G71" t="s">
         <v>285</v>
       </c>
-      <c r="G71" t="s">
+      <c r="H71" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -3646,19 +3872,22 @@
         <v>327</v>
       </c>
       <c r="D72" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E72" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F72" t="s">
+        <v>124</v>
+      </c>
+      <c r="G72" t="s">
         <v>286</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>82</v>
       </c>
@@ -3669,19 +3898,22 @@
         <v>318</v>
       </c>
       <c r="D73" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E73" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F73" t="s">
+        <v>124</v>
+      </c>
+      <c r="G73" t="s">
         <v>287</v>
       </c>
-      <c r="G73" t="s">
+      <c r="H73" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -3692,19 +3924,22 @@
         <v>319</v>
       </c>
       <c r="D74" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E74" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F74" t="s">
+        <v>124</v>
+      </c>
+      <c r="G74" t="s">
         <v>288</v>
       </c>
-      <c r="G74" t="s">
+      <c r="H74" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -3715,19 +3950,22 @@
         <v>320</v>
       </c>
       <c r="D75" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E75" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F75" t="s">
+        <v>124</v>
+      </c>
+      <c r="G75" t="s">
         <v>289</v>
       </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>85</v>
       </c>
@@ -3738,19 +3976,22 @@
         <v>321</v>
       </c>
       <c r="D76" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E76" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F76" t="s">
+        <v>124</v>
+      </c>
+      <c r="G76" t="s">
         <v>290</v>
       </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>86</v>
       </c>
@@ -3761,19 +4002,22 @@
         <v>322</v>
       </c>
       <c r="D77" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E77" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F77" t="s">
+        <v>124</v>
+      </c>
+      <c r="G77" t="s">
         <v>121</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>87</v>
       </c>
@@ -3784,19 +4028,22 @@
         <v>323</v>
       </c>
       <c r="D78" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E78" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F78" t="s">
+        <v>124</v>
+      </c>
+      <c r="G78" t="s">
         <v>291</v>
       </c>
-      <c r="G78" t="s">
+      <c r="H78" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>88</v>
       </c>
@@ -3807,19 +4054,22 @@
         <v>324</v>
       </c>
       <c r="D79" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E79" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F79" t="s">
+        <v>124</v>
+      </c>
+      <c r="G79" t="s">
         <v>292</v>
       </c>
-      <c r="G79" t="s">
+      <c r="H79" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>89</v>
       </c>
@@ -3830,19 +4080,22 @@
         <v>325</v>
       </c>
       <c r="D80" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E80" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F80" t="s">
+        <v>124</v>
+      </c>
+      <c r="G80" t="s">
         <v>293</v>
       </c>
-      <c r="G80" t="s">
+      <c r="H80" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>90</v>
       </c>
@@ -3853,19 +4106,22 @@
         <v>326</v>
       </c>
       <c r="D81" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E81" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F81" t="s">
+        <v>124</v>
+      </c>
+      <c r="G81" t="s">
         <v>294</v>
       </c>
-      <c r="G81" t="s">
+      <c r="H81" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>91</v>
       </c>
@@ -3876,19 +4132,22 @@
         <v>327</v>
       </c>
       <c r="D82" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E82" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F82" t="s">
+        <v>124</v>
+      </c>
+      <c r="G82" t="s">
         <v>295</v>
       </c>
-      <c r="G82" t="s">
+      <c r="H82" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>92</v>
       </c>
@@ -3899,19 +4158,22 @@
         <v>318</v>
       </c>
       <c r="D83" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E83" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F83" t="s">
+        <v>124</v>
+      </c>
+      <c r="G83" t="s">
         <v>296</v>
       </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>94</v>
       </c>
@@ -3922,19 +4184,22 @@
         <v>319</v>
       </c>
       <c r="D84" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E84" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F84" t="s">
+        <v>124</v>
+      </c>
+      <c r="G84" t="s">
         <v>297</v>
       </c>
-      <c r="G84" t="s">
+      <c r="H84" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>95</v>
       </c>
@@ -3945,19 +4210,22 @@
         <v>320</v>
       </c>
       <c r="D85" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E85" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F85" t="s">
+        <v>124</v>
+      </c>
+      <c r="G85" t="s">
         <v>298</v>
       </c>
-      <c r="G85" t="s">
+      <c r="H85" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>96</v>
       </c>
@@ -3968,19 +4236,22 @@
         <v>321</v>
       </c>
       <c r="D86" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E86" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F86" t="s">
+        <v>124</v>
+      </c>
+      <c r="G86" t="s">
         <v>299</v>
       </c>
-      <c r="G86" t="s">
+      <c r="H86" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>97</v>
       </c>
@@ -3991,19 +4262,22 @@
         <v>322</v>
       </c>
       <c r="D87" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E87" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F87" t="s">
+        <v>124</v>
+      </c>
+      <c r="G87" t="s">
         <v>300</v>
       </c>
-      <c r="G87" t="s">
+      <c r="H87" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>98</v>
       </c>
@@ -4014,19 +4288,22 @@
         <v>323</v>
       </c>
       <c r="D88" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E88" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F88" t="s">
+        <v>124</v>
+      </c>
+      <c r="G88" t="s">
         <v>301</v>
       </c>
-      <c r="G88" t="s">
+      <c r="H88" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>99</v>
       </c>
@@ -4037,19 +4314,22 @@
         <v>324</v>
       </c>
       <c r="D89" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E89" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F89" t="s">
+        <v>124</v>
+      </c>
+      <c r="G89" t="s">
         <v>302</v>
       </c>
-      <c r="G89" t="s">
+      <c r="H89" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>100</v>
       </c>
@@ -4060,19 +4340,22 @@
         <v>325</v>
       </c>
       <c r="D90" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E90" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F90" t="s">
+        <v>124</v>
+      </c>
+      <c r="G90" t="s">
         <v>303</v>
       </c>
-      <c r="G90" t="s">
+      <c r="H90" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>101</v>
       </c>
@@ -4083,19 +4366,22 @@
         <v>326</v>
       </c>
       <c r="D91" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E91" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F91" t="s">
+        <v>124</v>
+      </c>
+      <c r="G91" t="s">
         <v>304</v>
       </c>
-      <c r="G91" t="s">
+      <c r="H91" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>102</v>
       </c>
@@ -4106,19 +4392,22 @@
         <v>327</v>
       </c>
       <c r="D92" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E92" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F92" t="s">
+        <v>124</v>
+      </c>
+      <c r="G92" t="s">
         <v>305</v>
       </c>
-      <c r="G92" t="s">
+      <c r="H92" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>103</v>
       </c>
@@ -4129,19 +4418,22 @@
         <v>318</v>
       </c>
       <c r="D93" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E93" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F93" t="s">
+        <v>124</v>
+      </c>
+      <c r="G93" t="s">
         <v>306</v>
       </c>
-      <c r="G93" t="s">
+      <c r="H93" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>104</v>
       </c>
@@ -4152,19 +4444,22 @@
         <v>319</v>
       </c>
       <c r="D94" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E94" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F94" t="s">
+        <v>124</v>
+      </c>
+      <c r="G94" t="s">
         <v>307</v>
       </c>
-      <c r="G94" t="s">
+      <c r="H94" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>105</v>
       </c>
@@ -4175,19 +4470,22 @@
         <v>320</v>
       </c>
       <c r="D95" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E95" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F95" t="s">
+        <v>124</v>
+      </c>
+      <c r="G95" t="s">
         <v>308</v>
       </c>
-      <c r="G95" t="s">
+      <c r="H95" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>106</v>
       </c>
@@ -4198,19 +4496,22 @@
         <v>321</v>
       </c>
       <c r="D96" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E96" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F96" t="s">
+        <v>124</v>
+      </c>
+      <c r="G96" t="s">
         <v>309</v>
       </c>
-      <c r="G96" t="s">
+      <c r="H96" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>107</v>
       </c>
@@ -4221,19 +4522,22 @@
         <v>322</v>
       </c>
       <c r="D97" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E97" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F97" t="s">
+        <v>124</v>
+      </c>
+      <c r="G97" t="s">
         <v>310</v>
       </c>
-      <c r="G97" t="s">
+      <c r="H97" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>108</v>
       </c>
@@ -4244,19 +4548,22 @@
         <v>323</v>
       </c>
       <c r="D98" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E98" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F98" t="s">
+        <v>124</v>
+      </c>
+      <c r="G98" t="s">
         <v>311</v>
       </c>
-      <c r="G98" t="s">
+      <c r="H98" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>109</v>
       </c>
@@ -4267,19 +4574,22 @@
         <v>324</v>
       </c>
       <c r="D99" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E99" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F99" t="s">
+        <v>124</v>
+      </c>
+      <c r="G99" t="s">
         <v>312</v>
       </c>
-      <c r="G99" t="s">
+      <c r="H99" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>110</v>
       </c>
@@ -4290,19 +4600,22 @@
         <v>325</v>
       </c>
       <c r="D100" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E100" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F100" t="s">
+        <v>124</v>
+      </c>
+      <c r="G100" t="s">
         <v>313</v>
       </c>
-      <c r="G100" t="s">
+      <c r="H100" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>111</v>
       </c>
@@ -4313,19 +4626,22 @@
         <v>326</v>
       </c>
       <c r="D101" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E101" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F101" t="s">
+        <v>124</v>
+      </c>
+      <c r="G101" t="s">
         <v>314</v>
       </c>
-      <c r="G101" t="s">
+      <c r="H101" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>112</v>
       </c>
@@ -4336,15 +4652,18 @@
         <v>327</v>
       </c>
       <c r="D102" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E102" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F102" t="s">
+        <v>124</v>
+      </c>
+      <c r="G102" t="s">
         <v>315</v>
       </c>
-      <c r="G102" t="s">
+      <c r="H102" t="s">
         <v>93</v>
       </c>
     </row>
